--- a/dsa-doc/dsa-problems.xlsx
+++ b/dsa-doc/dsa-problems.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shubh\Projects\DSA\dsa-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD19E76-7BD8-4600-8A86-0166D598A4AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5CCE72D-94E8-45DF-8002-A8DB3CBF1DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="609">
   <si>
     <t>Num</t>
   </si>
@@ -1787,12 +1787,269 @@
   <si>
     <t>✉️ shubhamrathore1024@gmail.com</t>
   </si>
+  <si>
+    <t>Zodiac Sign</t>
+  </si>
+  <si>
+    <t>Sun</t>
+  </si>
+  <si>
+    <t>Moon</t>
+  </si>
+  <si>
+    <t>Mars</t>
+  </si>
+  <si>
+    <t>Mercury</t>
+  </si>
+  <si>
+    <t>Jupiter</t>
+  </si>
+  <si>
+    <t>Venus</t>
+  </si>
+  <si>
+    <t>Saturn</t>
+  </si>
+  <si>
+    <t>Total (SAV)</t>
+  </si>
+  <si>
+    <t>Strength</t>
+  </si>
+  <si>
+    <t>Aries (Ar)</t>
+  </si>
+  <si>
+    <t>Strong</t>
+  </si>
+  <si>
+    <t>Taurus (Ta)</t>
+  </si>
+  <si>
+    <t>Very Strong</t>
+  </si>
+  <si>
+    <t>Gemini (Ge)</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Cancer (Ca)</t>
+  </si>
+  <si>
+    <t>Below Average</t>
+  </si>
+  <si>
+    <t>Leo (Le)</t>
+  </si>
+  <si>
+    <t>Virgo (Vi)</t>
+  </si>
+  <si>
+    <t>Weak</t>
+  </si>
+  <si>
+    <t>Libra (Li)</t>
+  </si>
+  <si>
+    <t>Scorpio (Sc)</t>
+  </si>
+  <si>
+    <t>Sagittarius (Sa)</t>
+  </si>
+  <si>
+    <t>Above Average</t>
+  </si>
+  <si>
+    <t>Capricorn (Cp)</t>
+  </si>
+  <si>
+    <t>Aquarius (Aq)</t>
+  </si>
+  <si>
+    <t>Pisces (Pi)</t>
+  </si>
+  <si>
+    <t>Total Points</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Planet</t>
+  </si>
+  <si>
+    <t>Sign &amp; House</t>
+  </si>
+  <si>
+    <t>Individual Bindus (BAV)</t>
+  </si>
+  <si>
+    <t>SAV House Score</t>
+  </si>
+  <si>
+    <t>Practical Interpretation</t>
+  </si>
+  <si>
+    <t>Cancer (10th H)</t>
+  </si>
+  <si>
+    <t>Strong individual authority (5 points) in career; provides leadership and strong drive despite moderate house SAV.</t>
+  </si>
+  <si>
+    <t>Solid analytical and communication skills applied directly to professional workflows.</t>
+  </si>
+  <si>
+    <r>
+      <t>Cancer (10th H)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Debilitated)</t>
+    </r>
+  </si>
+  <si>
+    <t>Requires calculated action rather than impulse; energy is channeled into structured technical execution.</t>
+  </si>
+  <si>
+    <r>
+      <t>Cancer (10th H)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Exalted)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Core powerhouse.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Exalted with high individual bindus (6); acts as the primary guiding pillar for career growth, ethics, and mentorship.</t>
+    </r>
+  </si>
+  <si>
+    <t>Capricorn (4th H)</t>
+  </si>
+  <si>
+    <t>Stable emotional endurance and practical mindset toward home, stability, and family assets.</t>
+  </si>
+  <si>
+    <t>Leo (11th H)</t>
+  </si>
+  <si>
+    <t>Lagna lord sitting in the house of gains; brings steady income streams through focused, high-value skills.</t>
+  </si>
+  <si>
+    <t>Gemini (9th H)</t>
+  </si>
+  <si>
+    <t>High bindus (5) as Yogakaraka (rules 4th &amp; 5th); gives long-term luck through structured study, discipline, and persistent effort.</t>
+  </si>
+  <si>
+    <t>Rahu</t>
+  </si>
+  <si>
+    <t>Taurus (8th H)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Placed in your </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>highest SAV house</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>; grants deep analytical/research depth, sudden strategic advantages, and strong material resourcefulness.</t>
+    </r>
+  </si>
+  <si>
+    <t>Ketu</t>
+  </si>
+  <si>
+    <t>Scorpio (2nd H)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Placed in a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>strong SAV house</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>; protects accumulated assets and provides sharp, intuitive financial discernment.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1852,6 +2109,26 @@
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1897,7 +2174,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1920,12 +2197,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1972,6 +2264,15 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2253,7 +2554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:L205"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.21875" customWidth="1"/>
@@ -2262,6 +2563,7 @@
     <col min="4" max="4" width="50.5546875" customWidth="1"/>
     <col min="5" max="5" width="24.109375" customWidth="1"/>
     <col min="6" max="6" width="15.33203125" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26.4" customHeight="1" thickBot="1">
@@ -3320,7 +3622,9 @@
       <c r="E53" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F53" s="6"/>
+      <c r="F53" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="54" spans="1:6" ht="15" thickBot="1">
       <c r="A54" s="6">
@@ -3338,7 +3642,9 @@
       <c r="E54" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F54" s="6"/>
+      <c r="F54" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="55" spans="1:6" ht="15" thickBot="1">
       <c r="A55" s="6">
@@ -3356,7 +3662,9 @@
       <c r="E55" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F55" s="6"/>
+      <c r="F55" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="56" spans="1:6" ht="15" thickBot="1">
       <c r="A56" s="6">
@@ -3374,7 +3682,9 @@
       <c r="E56" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F56" s="6"/>
+      <c r="F56" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="57" spans="1:6" ht="15" thickBot="1">
       <c r="A57" s="6">
@@ -3392,7 +3702,9 @@
       <c r="E57" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F57" s="6"/>
+      <c r="F57" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="58" spans="1:6" ht="15" thickBot="1">
       <c r="A58" s="6">
@@ -3410,7 +3722,9 @@
       <c r="E58" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F58" s="6"/>
+      <c r="F58" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="59" spans="1:6" ht="15" thickBot="1">
       <c r="A59" s="6">
@@ -3428,7 +3742,9 @@
       <c r="E59" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F59" s="6"/>
+      <c r="F59" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="60" spans="1:6" ht="15" thickBot="1">
       <c r="A60" s="9">
@@ -3446,7 +3762,9 @@
       <c r="E60" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F60" s="9"/>
+      <c r="F60" s="9" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="61" spans="1:6" ht="15" thickBot="1">
       <c r="A61" s="9">
@@ -3464,7 +3782,9 @@
       <c r="E61" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F61" s="9"/>
+      <c r="F61" s="9" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="62" spans="1:6" ht="15" thickBot="1">
       <c r="A62" s="6">
@@ -3482,7 +3802,9 @@
       <c r="E62" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F62" s="6"/>
+      <c r="F62" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="63" spans="1:6" ht="15" thickBot="1">
       <c r="A63" s="6">
@@ -3500,7 +3822,9 @@
       <c r="E63" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F63" s="6"/>
+      <c r="F63" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="64" spans="1:6" ht="15" thickBot="1">
       <c r="A64" s="9">
@@ -3518,7 +3842,9 @@
       <c r="E64" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F64" s="9"/>
+      <c r="F64" s="9" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="65" spans="1:6" ht="15" thickBot="1">
       <c r="A65" s="4">
@@ -3536,7 +3862,9 @@
       <c r="E65" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F65" s="4"/>
+      <c r="F65" s="4" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="66" spans="1:6" ht="15" thickBot="1">
       <c r="A66" s="4">
@@ -3554,7 +3882,9 @@
       <c r="E66" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F66" s="4"/>
+      <c r="F66" s="4" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="67" spans="1:6" ht="15" thickBot="1">
       <c r="A67" s="6">
@@ -3572,7 +3902,9 @@
       <c r="E67" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F67" s="6"/>
+      <c r="F67" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="68" spans="1:6" ht="15" thickBot="1">
       <c r="A68" s="6">
@@ -3590,7 +3922,9 @@
       <c r="E68" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F68" s="6"/>
+      <c r="F68" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="69" spans="1:6" ht="15" thickBot="1">
       <c r="A69" s="6">
@@ -3608,7 +3942,9 @@
       <c r="E69" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F69" s="6"/>
+      <c r="F69" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="70" spans="1:6" ht="15" thickBot="1">
       <c r="A70" s="6">
@@ -3626,7 +3962,9 @@
       <c r="E70" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F70" s="6"/>
+      <c r="F70" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="71" spans="1:6" ht="15" thickBot="1">
       <c r="A71" s="9">
@@ -3644,7 +3982,9 @@
       <c r="E71" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F71" s="9"/>
+      <c r="F71" s="9" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="72" spans="1:6" ht="15" thickBot="1">
       <c r="A72" s="6">
@@ -3662,7 +4002,9 @@
       <c r="E72" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F72" s="6"/>
+      <c r="F72" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="73" spans="1:6" ht="15" thickBot="1">
       <c r="A73" s="6">
@@ -3680,7 +4022,9 @@
       <c r="E73" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F73" s="6"/>
+      <c r="F73" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="74" spans="1:6" ht="15" thickBot="1">
       <c r="A74" s="6">
@@ -3698,7 +4042,9 @@
       <c r="E74" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F74" s="6"/>
+      <c r="F74" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="75" spans="1:6" ht="15" thickBot="1">
       <c r="A75" s="6">
@@ -3716,7 +4062,9 @@
       <c r="E75" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F75" s="6"/>
+      <c r="F75" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="76" spans="1:6" ht="15" thickBot="1">
       <c r="A76" s="6">
@@ -5085,6 +5433,626 @@
         <v>15</v>
       </c>
       <c r="F151" s="6"/>
+    </row>
+    <row r="180" spans="3:12" ht="15" thickBot="1"/>
+    <row r="181" spans="3:12" ht="28.2" thickBot="1">
+      <c r="C181" s="18" t="s">
+        <v>555</v>
+      </c>
+      <c r="D181" s="18" t="s">
+        <v>556</v>
+      </c>
+      <c r="E181" s="18" t="s">
+        <v>557</v>
+      </c>
+      <c r="F181" s="18" t="s">
+        <v>558</v>
+      </c>
+      <c r="G181" s="18" t="s">
+        <v>559</v>
+      </c>
+      <c r="H181" s="18" t="s">
+        <v>560</v>
+      </c>
+      <c r="I181" s="18" t="s">
+        <v>561</v>
+      </c>
+      <c r="J181" s="18" t="s">
+        <v>562</v>
+      </c>
+      <c r="K181" s="18" t="s">
+        <v>563</v>
+      </c>
+      <c r="L181" s="18" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="182" spans="3:12" ht="15" thickBot="1">
+      <c r="C182" s="18" t="s">
+        <v>565</v>
+      </c>
+      <c r="D182" s="19">
+        <v>4</v>
+      </c>
+      <c r="E182" s="19">
+        <v>6</v>
+      </c>
+      <c r="F182" s="19">
+        <v>4</v>
+      </c>
+      <c r="G182" s="19">
+        <v>5</v>
+      </c>
+      <c r="H182" s="19">
+        <v>6</v>
+      </c>
+      <c r="I182" s="19">
+        <v>4</v>
+      </c>
+      <c r="J182" s="19">
+        <v>4</v>
+      </c>
+      <c r="K182" s="18">
+        <v>33</v>
+      </c>
+      <c r="L182" s="19" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="183" spans="3:12" ht="28.2" thickBot="1">
+      <c r="C183" s="18" t="s">
+        <v>567</v>
+      </c>
+      <c r="D183" s="19">
+        <v>4</v>
+      </c>
+      <c r="E183" s="19">
+        <v>5</v>
+      </c>
+      <c r="F183" s="19">
+        <v>4</v>
+      </c>
+      <c r="G183" s="19">
+        <v>5</v>
+      </c>
+      <c r="H183" s="19">
+        <v>7</v>
+      </c>
+      <c r="I183" s="19">
+        <v>7</v>
+      </c>
+      <c r="J183" s="19">
+        <v>4</v>
+      </c>
+      <c r="K183" s="18">
+        <v>36</v>
+      </c>
+      <c r="L183" s="19" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="184" spans="3:12" ht="28.2" thickBot="1">
+      <c r="C184" s="18" t="s">
+        <v>569</v>
+      </c>
+      <c r="D184" s="19">
+        <v>3</v>
+      </c>
+      <c r="E184" s="19">
+        <v>3</v>
+      </c>
+      <c r="F184" s="19">
+        <v>4</v>
+      </c>
+      <c r="G184" s="19">
+        <v>6</v>
+      </c>
+      <c r="H184" s="19">
+        <v>2</v>
+      </c>
+      <c r="I184" s="19">
+        <v>4</v>
+      </c>
+      <c r="J184" s="19">
+        <v>5</v>
+      </c>
+      <c r="K184" s="18">
+        <v>27</v>
+      </c>
+      <c r="L184" s="19" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="185" spans="3:12" ht="42" thickBot="1">
+      <c r="C185" s="18" t="s">
+        <v>571</v>
+      </c>
+      <c r="D185" s="19">
+        <v>5</v>
+      </c>
+      <c r="E185" s="19">
+        <v>4</v>
+      </c>
+      <c r="F185" s="19">
+        <v>3</v>
+      </c>
+      <c r="G185" s="19">
+        <v>4</v>
+      </c>
+      <c r="H185" s="19">
+        <v>6</v>
+      </c>
+      <c r="I185" s="19">
+        <v>0</v>
+      </c>
+      <c r="J185" s="19">
+        <v>3</v>
+      </c>
+      <c r="K185" s="18">
+        <v>25</v>
+      </c>
+      <c r="L185" s="19" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="186" spans="3:12" ht="42" thickBot="1">
+      <c r="C186" s="18" t="s">
+        <v>573</v>
+      </c>
+      <c r="D186" s="19">
+        <v>3</v>
+      </c>
+      <c r="E186" s="19">
+        <v>3</v>
+      </c>
+      <c r="F186" s="19">
+        <v>2</v>
+      </c>
+      <c r="G186" s="19">
+        <v>4</v>
+      </c>
+      <c r="H186" s="19">
+        <v>6</v>
+      </c>
+      <c r="I186" s="19">
+        <v>4</v>
+      </c>
+      <c r="J186" s="19">
+        <v>3</v>
+      </c>
+      <c r="K186" s="18">
+        <v>25</v>
+      </c>
+      <c r="L186" s="19" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="187" spans="3:12" ht="15" thickBot="1">
+      <c r="C187" s="18" t="s">
+        <v>574</v>
+      </c>
+      <c r="D187" s="19">
+        <v>3</v>
+      </c>
+      <c r="E187" s="19">
+        <v>3</v>
+      </c>
+      <c r="F187" s="19">
+        <v>3</v>
+      </c>
+      <c r="G187" s="19">
+        <v>3</v>
+      </c>
+      <c r="H187" s="19">
+        <v>4</v>
+      </c>
+      <c r="I187" s="19">
+        <v>5</v>
+      </c>
+      <c r="J187" s="19">
+        <v>1</v>
+      </c>
+      <c r="K187" s="18">
+        <v>22</v>
+      </c>
+      <c r="L187" s="19" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="188" spans="3:12" ht="42" thickBot="1">
+      <c r="C188" s="18" t="s">
+        <v>576</v>
+      </c>
+      <c r="D188" s="19">
+        <v>3</v>
+      </c>
+      <c r="E188" s="19">
+        <v>5</v>
+      </c>
+      <c r="F188" s="19">
+        <v>2</v>
+      </c>
+      <c r="G188" s="19">
+        <v>4</v>
+      </c>
+      <c r="H188" s="19">
+        <v>6</v>
+      </c>
+      <c r="I188" s="19">
+        <v>3</v>
+      </c>
+      <c r="J188" s="19">
+        <v>3</v>
+      </c>
+      <c r="K188" s="18">
+        <v>26</v>
+      </c>
+      <c r="L188" s="19" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="189" spans="3:12" ht="15" thickBot="1">
+      <c r="C189" s="18" t="s">
+        <v>577</v>
+      </c>
+      <c r="D189" s="19">
+        <v>3</v>
+      </c>
+      <c r="E189" s="19">
+        <v>5</v>
+      </c>
+      <c r="F189" s="19">
+        <v>3</v>
+      </c>
+      <c r="G189" s="19">
+        <v>5</v>
+      </c>
+      <c r="H189" s="19">
+        <v>4</v>
+      </c>
+      <c r="I189" s="19">
+        <v>6</v>
+      </c>
+      <c r="J189" s="19">
+        <v>4</v>
+      </c>
+      <c r="K189" s="18">
+        <v>30</v>
+      </c>
+      <c r="L189" s="19" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="190" spans="3:12" ht="42" thickBot="1">
+      <c r="C190" s="18" t="s">
+        <v>578</v>
+      </c>
+      <c r="D190" s="19">
+        <v>4</v>
+      </c>
+      <c r="E190" s="19">
+        <v>4</v>
+      </c>
+      <c r="F190" s="19">
+        <v>5</v>
+      </c>
+      <c r="G190" s="19">
+        <v>5</v>
+      </c>
+      <c r="H190" s="19">
+        <v>2</v>
+      </c>
+      <c r="I190" s="19">
+        <v>5</v>
+      </c>
+      <c r="J190" s="19">
+        <v>4</v>
+      </c>
+      <c r="K190" s="18">
+        <v>29</v>
+      </c>
+      <c r="L190" s="19" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="191" spans="3:12" ht="42" thickBot="1">
+      <c r="C191" s="18" t="s">
+        <v>580</v>
+      </c>
+      <c r="D191" s="19">
+        <v>5</v>
+      </c>
+      <c r="E191" s="19">
+        <v>4</v>
+      </c>
+      <c r="F191" s="19">
+        <v>3</v>
+      </c>
+      <c r="G191" s="19">
+        <v>3</v>
+      </c>
+      <c r="H191" s="19">
+        <v>5</v>
+      </c>
+      <c r="I191" s="19">
+        <v>3</v>
+      </c>
+      <c r="J191" s="19">
+        <v>3</v>
+      </c>
+      <c r="K191" s="18">
+        <v>26</v>
+      </c>
+      <c r="L191" s="19" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="192" spans="3:12" ht="42" thickBot="1">
+      <c r="C192" s="18" t="s">
+        <v>581</v>
+      </c>
+      <c r="D192" s="19">
+        <v>4</v>
+      </c>
+      <c r="E192" s="19">
+        <v>4</v>
+      </c>
+      <c r="F192" s="19">
+        <v>2</v>
+      </c>
+      <c r="G192" s="19">
+        <v>4</v>
+      </c>
+      <c r="H192" s="19">
+        <v>5</v>
+      </c>
+      <c r="I192" s="19">
+        <v>5</v>
+      </c>
+      <c r="J192" s="19">
+        <v>2</v>
+      </c>
+      <c r="K192" s="18">
+        <v>26</v>
+      </c>
+      <c r="L192" s="19" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="193" spans="3:12" ht="15" thickBot="1">
+      <c r="C193" s="18" t="s">
+        <v>582</v>
+      </c>
+      <c r="D193" s="19">
+        <v>7</v>
+      </c>
+      <c r="E193" s="19">
+        <v>3</v>
+      </c>
+      <c r="F193" s="19">
+        <v>4</v>
+      </c>
+      <c r="G193" s="19">
+        <v>6</v>
+      </c>
+      <c r="H193" s="19">
+        <v>3</v>
+      </c>
+      <c r="I193" s="19">
+        <v>6</v>
+      </c>
+      <c r="J193" s="19">
+        <v>3</v>
+      </c>
+      <c r="K193" s="18">
+        <v>32</v>
+      </c>
+      <c r="L193" s="19" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="194" spans="3:12" ht="15" thickBot="1">
+      <c r="C194" s="18" t="s">
+        <v>583</v>
+      </c>
+      <c r="D194" s="18">
+        <v>48</v>
+      </c>
+      <c r="E194" s="18">
+        <v>49</v>
+      </c>
+      <c r="F194" s="18">
+        <v>39</v>
+      </c>
+      <c r="G194" s="18">
+        <v>54</v>
+      </c>
+      <c r="H194" s="18">
+        <v>56</v>
+      </c>
+      <c r="I194" s="18">
+        <v>52</v>
+      </c>
+      <c r="J194" s="18">
+        <v>39</v>
+      </c>
+      <c r="K194" s="18">
+        <v>337</v>
+      </c>
+      <c r="L194" s="19" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="195" spans="3:12" ht="15" thickBot="1"/>
+    <row r="196" spans="3:12" ht="69.599999999999994" thickBot="1">
+      <c r="C196" s="18" t="s">
+        <v>585</v>
+      </c>
+      <c r="D196" s="18" t="s">
+        <v>586</v>
+      </c>
+      <c r="E196" s="18" t="s">
+        <v>587</v>
+      </c>
+      <c r="F196" s="18" t="s">
+        <v>588</v>
+      </c>
+      <c r="G196" s="18" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="197" spans="3:12" ht="262.8" thickBot="1">
+      <c r="C197" s="18" t="s">
+        <v>556</v>
+      </c>
+      <c r="D197" s="18" t="s">
+        <v>590</v>
+      </c>
+      <c r="E197" s="20">
+        <v>46239</v>
+      </c>
+      <c r="F197" s="18">
+        <v>25</v>
+      </c>
+      <c r="G197" s="19" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="198" spans="3:12" ht="180" thickBot="1">
+      <c r="C198" s="18" t="s">
+        <v>559</v>
+      </c>
+      <c r="D198" s="18" t="s">
+        <v>590</v>
+      </c>
+      <c r="E198" s="20">
+        <v>46238</v>
+      </c>
+      <c r="F198" s="18">
+        <v>25</v>
+      </c>
+      <c r="G198" s="19" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="199" spans="3:12" ht="262.8" thickBot="1">
+      <c r="C199" s="18" t="s">
+        <v>558</v>
+      </c>
+      <c r="D199" s="18" t="s">
+        <v>593</v>
+      </c>
+      <c r="E199" s="20">
+        <v>46237</v>
+      </c>
+      <c r="F199" s="18">
+        <v>25</v>
+      </c>
+      <c r="G199" s="19" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="200" spans="3:12" ht="304.2" thickBot="1">
+      <c r="C200" s="18" t="s">
+        <v>560</v>
+      </c>
+      <c r="D200" s="18" t="s">
+        <v>595</v>
+      </c>
+      <c r="E200" s="20">
+        <v>46240</v>
+      </c>
+      <c r="F200" s="18">
+        <v>25</v>
+      </c>
+      <c r="G200" s="18" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="201" spans="3:12" ht="221.4" thickBot="1">
+      <c r="C201" s="18" t="s">
+        <v>557</v>
+      </c>
+      <c r="D201" s="18" t="s">
+        <v>597</v>
+      </c>
+      <c r="E201" s="20">
+        <v>46238</v>
+      </c>
+      <c r="F201" s="18">
+        <v>26</v>
+      </c>
+      <c r="G201" s="19" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="202" spans="3:12" ht="249" thickBot="1">
+      <c r="C202" s="18" t="s">
+        <v>561</v>
+      </c>
+      <c r="D202" s="18" t="s">
+        <v>599</v>
+      </c>
+      <c r="E202" s="20">
+        <v>46238</v>
+      </c>
+      <c r="F202" s="18">
+        <v>25</v>
+      </c>
+      <c r="G202" s="19" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="203" spans="3:12" ht="318" thickBot="1">
+      <c r="C203" s="18" t="s">
+        <v>562</v>
+      </c>
+      <c r="D203" s="18" t="s">
+        <v>601</v>
+      </c>
+      <c r="E203" s="20">
+        <v>46239</v>
+      </c>
+      <c r="F203" s="18">
+        <v>27</v>
+      </c>
+      <c r="G203" s="19" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="204" spans="3:12" ht="318" thickBot="1">
+      <c r="C204" s="18" t="s">
+        <v>603</v>
+      </c>
+      <c r="D204" s="18" t="s">
+        <v>604</v>
+      </c>
+      <c r="E204" s="19" t="s">
+        <v>584</v>
+      </c>
+      <c r="F204" s="18">
+        <v>36</v>
+      </c>
+      <c r="G204" s="19" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="205" spans="3:12" ht="276.60000000000002" thickBot="1">
+      <c r="C205" s="18" t="s">
+        <v>606</v>
+      </c>
+      <c r="D205" s="18" t="s">
+        <v>607</v>
+      </c>
+      <c r="E205" s="19" t="s">
+        <v>584</v>
+      </c>
+      <c r="F205" s="18">
+        <v>30</v>
+      </c>
+      <c r="G205" s="19" t="s">
+        <v>608</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/dsa-doc/dsa-problems.xlsx
+++ b/dsa-doc/dsa-problems.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shubh\Projects\DSA\dsa-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5CCE72D-94E8-45DF-8002-A8DB3CBF1DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8493EA0D-F9C7-4481-85B8-9D85D4E0A9FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="625">
   <si>
     <t>Num</t>
   </si>
@@ -2044,12 +2044,60 @@
       <t>; protects accumulated assets and provides sharp, intuitive financial discernment.</t>
     </r>
   </si>
+  <si>
+    <t>Kafka and Spring related questions.</t>
+  </si>
+  <si>
+    <t>Dependency Injection?</t>
+  </si>
+  <si>
+    <t>What is a good unit test?</t>
+  </si>
+  <si>
+    <t>Difference between trigger and procedure</t>
+  </si>
+  <si>
+    <t> Object types in java 2. Hybernate and spring boot prep</t>
+  </si>
+  <si>
+    <t>Interview</t>
+  </si>
+  <si>
+    <t>Core java, spring boot basic question. More DB related questions design patterns worked little bit on the problem solving Core java, spring boot basic question. More DB related questions design patterns worked little bit on the problem solving</t>
+  </si>
+  <si>
+    <t>Interview questions [1]</t>
+  </si>
+  <si>
+    <t>Question 1</t>
+  </si>
+  <si>
+    <t>Design patterns, tricky questions on the join tables.</t>
+  </si>
+  <si>
+    <t>Have you used java? How do you feel about Kafka and have you used Redpanda Kafka? How do you feel about picking up new technologies?</t>
+  </si>
+  <si>
+    <t>General experience and vague systems design question</t>
+  </si>
+  <si>
+    <t>Explain a real time simulation of multithreading</t>
+  </si>
+  <si>
+    <t>Plabeeta</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/permutations/solutions/18239/a-general-approach-to-backtracking-quest-e6b1</t>
+  </si>
+  <si>
+    <t>Backtracking helper</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2129,6 +2177,30 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF384148"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF384148"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF647380"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -2174,7 +2246,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2212,12 +2284,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2272,6 +2355,20 @@
     </xf>
     <xf numFmtId="16" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3846,7 +3943,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="15" thickBot="1">
+    <row r="65" spans="1:7" ht="15" thickBot="1">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -3866,7 +3963,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="15" thickBot="1">
+    <row r="66" spans="1:7" ht="15" thickBot="1">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -3886,7 +3983,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="15" thickBot="1">
+    <row r="67" spans="1:7" ht="15" thickBot="1">
       <c r="A67" s="6">
         <v>66</v>
       </c>
@@ -3906,7 +4003,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="15" thickBot="1">
+    <row r="68" spans="1:7" ht="15" thickBot="1">
       <c r="A68" s="6">
         <v>67</v>
       </c>
@@ -3926,7 +4023,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="15" thickBot="1">
+    <row r="69" spans="1:7" ht="15" thickBot="1">
       <c r="A69" s="6">
         <v>68</v>
       </c>
@@ -3946,7 +4043,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="15" thickBot="1">
+    <row r="70" spans="1:7" ht="15" thickBot="1">
       <c r="A70" s="6">
         <v>69</v>
       </c>
@@ -3966,7 +4063,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="15" thickBot="1">
+    <row r="71" spans="1:7" ht="15" thickBot="1">
       <c r="A71" s="9">
         <v>70</v>
       </c>
@@ -3985,8 +4082,11 @@
       <c r="F71" s="9" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" ht="15" thickBot="1">
+      <c r="G71" s="26" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="15" thickBot="1">
       <c r="A72" s="6">
         <v>71</v>
       </c>
@@ -4005,8 +4105,11 @@
       <c r="F72" s="6" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" ht="15" thickBot="1">
+      <c r="G72" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="15" thickBot="1">
       <c r="A73" s="6">
         <v>72</v>
       </c>
@@ -4026,7 +4129,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="15" thickBot="1">
+    <row r="74" spans="1:7" ht="15" thickBot="1">
       <c r="A74" s="6">
         <v>73</v>
       </c>
@@ -4046,7 +4149,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="15" thickBot="1">
+    <row r="75" spans="1:7" ht="15" thickBot="1">
       <c r="A75" s="6">
         <v>74</v>
       </c>
@@ -4066,7 +4169,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="15" thickBot="1">
+    <row r="76" spans="1:7" ht="15" thickBot="1">
       <c r="A76" s="6">
         <v>75</v>
       </c>
@@ -4082,9 +4185,11 @@
       <c r="E76" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F76" s="6"/>
-    </row>
-    <row r="77" spans="1:6" ht="15" thickBot="1">
+      <c r="F76" s="6" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="15" thickBot="1">
       <c r="A77" s="6">
         <v>76</v>
       </c>
@@ -4100,9 +4205,11 @@
       <c r="E77" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F77" s="6"/>
-    </row>
-    <row r="78" spans="1:6" ht="15" thickBot="1">
+      <c r="F77" s="6" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="15" thickBot="1">
       <c r="A78" s="6">
         <v>77</v>
       </c>
@@ -4118,9 +4225,11 @@
       <c r="E78" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F78" s="6"/>
-    </row>
-    <row r="79" spans="1:6" ht="15" thickBot="1">
+      <c r="F78" s="6" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="15" thickBot="1">
       <c r="A79" s="6">
         <v>78</v>
       </c>
@@ -4138,7 +4247,7 @@
       </c>
       <c r="F79" s="6"/>
     </row>
-    <row r="80" spans="1:6" ht="15" thickBot="1">
+    <row r="80" spans="1:7" ht="15" thickBot="1">
       <c r="A80" s="9">
         <v>79</v>
       </c>
@@ -5433,6 +5542,60 @@
         <v>15</v>
       </c>
       <c r="F151" s="6"/>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="C155" s="21" t="s">
+        <v>609</v>
+      </c>
+      <c r="D155" s="21" t="s">
+        <v>610</v>
+      </c>
+      <c r="E155" s="21" t="s">
+        <v>611</v>
+      </c>
+      <c r="F155" s="21" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="C156" s="21" t="s">
+        <v>613</v>
+      </c>
+      <c r="D156" s="22" t="s">
+        <v>614</v>
+      </c>
+      <c r="E156" s="21" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" ht="40.799999999999997">
+      <c r="D157" s="23" t="s">
+        <v>615</v>
+      </c>
+      <c r="E157" s="21" t="s">
+        <v>620</v>
+      </c>
+      <c r="F157" s="21" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="D158" s="22" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="C159" s="25" t="s">
+        <v>622</v>
+      </c>
+      <c r="D159" s="24" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="D160" s="23" t="s">
+        <v>618</v>
+      </c>
     </row>
     <row r="180" spans="3:12" ht="15" thickBot="1"/>
     <row r="181" spans="3:12" ht="28.2" thickBot="1">
@@ -5884,7 +6047,7 @@
       </c>
     </row>
     <row r="195" spans="3:12" ht="15" thickBot="1"/>
-    <row r="196" spans="3:12" ht="69.599999999999994" thickBot="1">
+    <row r="196" spans="3:12" ht="42" thickBot="1">
       <c r="C196" s="18" t="s">
         <v>585</v>
       </c>
@@ -5901,7 +6064,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="197" spans="3:12" ht="262.8" thickBot="1">
+    <row r="197" spans="3:12" ht="152.4" thickBot="1">
       <c r="C197" s="18" t="s">
         <v>556</v>
       </c>
@@ -5918,7 +6081,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="198" spans="3:12" ht="180" thickBot="1">
+    <row r="198" spans="3:12" ht="124.8" thickBot="1">
       <c r="C198" s="18" t="s">
         <v>559</v>
       </c>
@@ -5935,7 +6098,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="199" spans="3:12" ht="262.8" thickBot="1">
+    <row r="199" spans="3:12" ht="152.4" thickBot="1">
       <c r="C199" s="18" t="s">
         <v>558</v>
       </c>
@@ -5952,7 +6115,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="200" spans="3:12" ht="304.2" thickBot="1">
+    <row r="200" spans="3:12" ht="180" thickBot="1">
       <c r="C200" s="18" t="s">
         <v>560</v>
       </c>
@@ -5969,7 +6132,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="201" spans="3:12" ht="221.4" thickBot="1">
+    <row r="201" spans="3:12" ht="138.6" thickBot="1">
       <c r="C201" s="18" t="s">
         <v>557</v>
       </c>
@@ -5986,7 +6149,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="202" spans="3:12" ht="249" thickBot="1">
+    <row r="202" spans="3:12" ht="152.4" thickBot="1">
       <c r="C202" s="18" t="s">
         <v>561</v>
       </c>
@@ -6003,7 +6166,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="203" spans="3:12" ht="318" thickBot="1">
+    <row r="203" spans="3:12" ht="180" thickBot="1">
       <c r="C203" s="18" t="s">
         <v>562</v>
       </c>
@@ -6020,7 +6183,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="204" spans="3:12" ht="318" thickBot="1">
+    <row r="204" spans="3:12" ht="180" thickBot="1">
       <c r="C204" s="18" t="s">
         <v>603</v>
       </c>
@@ -6037,7 +6200,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="205" spans="3:12" ht="276.60000000000002" thickBot="1">
+    <row r="205" spans="3:12" ht="152.4" thickBot="1">
       <c r="C205" s="18" t="s">
         <v>606</v>
       </c>

--- a/dsa-doc/dsa-problems.xlsx
+++ b/dsa-doc/dsa-problems.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shubh\Projects\DSA\dsa-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8493EA0D-F9C7-4481-85B8-9D85D4E0A9FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{967A0476-C9B4-4879-8A1E-BBBE26CB7861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Leetcode" sheetId="1" r:id="rId1"/>
+    <sheet name="Interview Questions" sheetId="3" r:id="rId2"/>
+    <sheet name="Resume Points" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="695">
   <si>
     <t>Num</t>
   </si>
@@ -42,9 +44,6 @@
   </si>
   <si>
     <t>Difficulty</t>
-  </si>
-  <si>
-    <t>Contains Duplicate</t>
   </si>
   <si>
     <t>Arrays &amp; Hashing</t>
@@ -2092,12 +2091,245 @@
   <si>
     <t>Backtracking helper</t>
   </si>
+  <si>
+    <t>Contains Duplicate+B49B53B2:B59B2:B67B2:B80</t>
+  </si>
+  <si>
+    <t>Minimum spanning tree ques</t>
+  </si>
+  <si>
+    <t>787. Cheapest Flights Within K Stops</t>
+  </si>
+  <si>
+    <t>778. Swim in Rising Water</t>
+  </si>
+  <si>
+    <t>815. Bus Routes</t>
+  </si>
+  <si>
+    <t>1091. Shortest Path in Binary Matrix</t>
+  </si>
+  <si>
+    <t>1631. Path With Minimum Effort</t>
+  </si>
+  <si>
+    <t>2812. Find the Safest Path in a Grid</t>
+  </si>
+  <si>
+    <t>2642. Design Graph With Shortest Path Calculator</t>
+  </si>
+  <si>
+    <t>Things needs to learn</t>
+  </si>
+  <si>
+    <t>We analysed our API latency and realized processing document evaluations sequentially was causing bottlenecks. I optimized the backend data paths by leveraging Java Stream APIs and Multithreading to handle validation sub-cases in parallel, which significantly cut down the processing time per case.</t>
+  </si>
+  <si>
+    <t>We have project related to it. We need to find out how much time its taking and how we resolve it</t>
+  </si>
+  <si>
+    <t>While our dedicated DevOps team manages the core cloud infrastructure , my responsibility is ensuring our code is deployment-ready. I coordinate with them to verify our microservice configurations, double-check that our multi-stage Docker builds pass successfully, and use basic Kubernetes commands to inspect logs and ensure healthy pod rolling updates during live releases.</t>
+  </si>
+  <si>
+    <t>We need to understand and take a look at this docker thing brother</t>
+  </si>
+  <si>
+    <t>When reviewing PRs, I don't just look for working code; I guide junior developers on best practices like keeping pull requests small and isolated, utilizing proper exception handling for our asynchronous Kafka events, and ensuring robust JUnit/Mockito test coverage before anything gets merged into our main branch</t>
+  </si>
+  <si>
+    <t>We need to have a demo plan for this to understand what could be common problems faced by developers in real life</t>
+  </si>
+  <si>
+    <t>I built a modular multistep wizard in React.</t>
+  </si>
+  <si>
+    <t>We need to talk about this more + we must make UI for our application</t>
+  </si>
+  <si>
+    <t>This maps perfectly back to the PostgreSQL talk track we built earlier. You can say: "When loan volume spiked, our relational databases experienced locking issues during heavy transactional updates. I worked on optimizing our repository layers, applying composite indexing on frequently joined tables, and using database execution plans (EXPLAIN) to catch unindexed sequential scans. This fixed the bottlenecks and pulled our query latency down drastically.</t>
+  </si>
+  <si>
+    <t>Need to learn how to optimize the sql queries</t>
+  </si>
+  <si>
+    <t>DSA/Coding</t>
+  </si>
+  <si>
+    <t>1. Find the middle node of a linked list in one pass.</t>
+  </si>
+  <si>
+    <t>2. Print the left view of a binary tree.</t>
+  </si>
+  <si>
+    <t>3. Detect a cycle in a graph.</t>
+  </si>
+  <si>
+    <t>4. Find the Nth Fibonacci number.</t>
+  </si>
+  <si>
+    <t>5. Merge overlapping intervals.</t>
+  </si>
+  <si>
+    <t>6. Reverse a linked list in groups of K.</t>
+  </si>
+  <si>
+    <t>7. Find the Longest Common Subsequence between two strings.</t>
+  </si>
+  <si>
+    <t>8. Check whether a binary tree is height-balanced.</t>
+  </si>
+  <si>
+    <t>9. Find the Kth largest element in an unsorted array.</t>
+  </si>
+  <si>
+    <t>10. Use multithreading to compute two sums and multiply their results.</t>
+  </si>
+  <si>
+    <t>Database (SQL)</t>
+  </si>
+  <si>
+    <t>1. Difference between clustered and non-clustered indexes.</t>
+  </si>
+  <si>
+    <t>2. Find duplicate records without using GROUP BY.</t>
+  </si>
+  <si>
+    <t>3. Find the second-highest salary without using LIMIT or TOP.</t>
+  </si>
+  <si>
+    <t>4. Design a database schema for a trade settlement system.</t>
+  </si>
+  <si>
+    <t>Web/Frameworks</t>
+  </si>
+  <si>
+    <t>1. How does @Transactional work internally in Spring, and why can it fail on private or protected methods?</t>
+  </si>
+  <si>
+    <t>2. Difference between ExecutorService, ForkJoinPool, and a plain Thread.</t>
+  </si>
+  <si>
+    <t>3. How do you make a HashMap thread-safe without using ConcurrentHashMap?</t>
+  </si>
+  <si>
+    <t>4. Difference between @Async and a manually managed thread pool in Spring.</t>
+  </si>
+  <si>
+    <t>5. How does Spring resolve autowiring when multiple beans of the same type exist?</t>
+  </si>
+  <si>
+    <t>6. What is a circuit breaker, and how does it differ from a bulkhead?</t>
+  </si>
+  <si>
+    <t>7. Difference between Kafka and a traditional message queue like ActiveMQ.</t>
+  </si>
+  <si>
+    <t>8. How would you design an idempotent Kafka consumer?</t>
+  </si>
+  <si>
+    <t>System Design</t>
+  </si>
+  <si>
+    <t>1. Explain the architecture of one of your recent projects.</t>
+  </si>
+  <si>
+    <t>2. Design a real-time fraud detection system for card transactions.</t>
+  </si>
+  <si>
+    <t>3. Design a trade settlement system that reconciles trades across multiple exchanges.</t>
+  </si>
+  <si>
+    <t>4. Design an auditable payment ledger that retains records for years.</t>
+  </si>
+  <si>
+    <t>5. Design a system to process millions of transactions within an overnight batch window.</t>
+  </si>
+  <si>
+    <t>Server/System</t>
+  </si>
+  <si>
+    <t>1. How do you capture and analyze a JVM heap dump to find a production memory leak?</t>
+  </si>
+  <si>
+    <t>2. How would you debug a thread stuck while holding a lock under high load?</t>
+  </si>
+  <si>
+    <t>3. How would you diagnose a sudden CPU spike without recent code changes?</t>
+  </si>
+  <si>
+    <t>4. How would you investigate a JVM crash that occurred overnight?</t>
+  </si>
+  <si>
+    <t>Prefix</t>
+  </si>
+  <si>
+    <t>Sorted Prefix</t>
+  </si>
+  <si>
+    <t>Two Sequences</t>
+  </si>
+  <si>
+    <t>Interval</t>
+  </si>
+  <si>
+    <t>Grid</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>DP pattern</t>
+  </si>
+  <si>
+    <t>Problems</t>
+  </si>
+  <si>
+    <t>Prefix DP</t>
+  </si>
+  <si>
+    <t>Job Scheduling, Box Stacking, Longest Chain, LIS Problems</t>
+  </si>
+  <si>
+    <t>Edit Distance, Longest Common Subsequence</t>
+  </si>
+  <si>
+    <t>Matrix Chain, Burst Balloons, Palindrome Problems</t>
+  </si>
+  <si>
+    <t>Unique Paths, Minimum Path Sum, Maximal Square</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Subproblem: First </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Elements</t>
+    </r>
+  </si>
+  <si>
+    <t>Coin Change, Climbing Stairs, House Robber, Decode Ways, Partition Equal Subset Sum (416)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2201,6 +2433,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -2246,7 +2486,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -2295,12 +2535,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFA3A3A3"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFA3A3A3"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFA3A3A3"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFA3A3A3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2369,6 +2624,19 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2680,7 +2948,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" thickBot="1">
@@ -2688,19 +2956,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>624</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="F2" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" thickBot="1">
@@ -2708,19 +2976,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" thickBot="1">
@@ -2728,19 +2996,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="E4" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" thickBot="1">
@@ -2748,19 +3016,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>14</v>
-      </c>
       <c r="E5" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" thickBot="1">
@@ -2768,19 +3036,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>17</v>
-      </c>
       <c r="E6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" thickBot="1">
@@ -2788,19 +3056,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="E7" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" thickBot="1">
@@ -2808,19 +3076,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>21</v>
-      </c>
       <c r="E8" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" thickBot="1">
@@ -2828,19 +3096,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>23</v>
-      </c>
       <c r="E9" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" thickBot="1">
@@ -2848,19 +3116,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>25</v>
-      </c>
       <c r="E10" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" thickBot="1">
@@ -2868,19 +3136,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="E11" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" thickBot="1">
@@ -2888,19 +3156,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>30</v>
-      </c>
       <c r="E12" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" thickBot="1">
@@ -2908,19 +3176,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>32</v>
-      </c>
       <c r="E13" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" thickBot="1">
@@ -2928,19 +3196,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>34</v>
-      </c>
       <c r="E14" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" thickBot="1">
@@ -2948,19 +3216,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="F15" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" thickBot="1">
@@ -2968,19 +3236,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="D16" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>40</v>
-      </c>
       <c r="E16" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" thickBot="1">
@@ -2988,19 +3256,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>42</v>
-      </c>
       <c r="E17" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" thickBot="1">
@@ -3008,19 +3276,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>44</v>
-      </c>
       <c r="E18" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" thickBot="1">
@@ -3028,19 +3296,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>46</v>
-      </c>
       <c r="E19" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" thickBot="1">
@@ -3048,19 +3316,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>48</v>
-      </c>
       <c r="E20" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" thickBot="1">
@@ -3068,19 +3336,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>50</v>
-      </c>
       <c r="E21" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" thickBot="1">
@@ -3088,19 +3356,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="D22" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="E22" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" thickBot="1">
@@ -3108,19 +3376,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>55</v>
-      </c>
       <c r="E23" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" thickBot="1">
@@ -3128,19 +3396,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>57</v>
-      </c>
       <c r="E24" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15" thickBot="1">
@@ -3148,19 +3416,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>59</v>
-      </c>
       <c r="E25" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" thickBot="1">
@@ -3168,19 +3436,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>61</v>
-      </c>
       <c r="E26" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" thickBot="1">
@@ -3188,19 +3456,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>63</v>
-      </c>
       <c r="E27" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" thickBot="1">
@@ -3208,19 +3476,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>65</v>
-      </c>
       <c r="E28" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" thickBot="1">
@@ -3228,19 +3496,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>67</v>
-      </c>
       <c r="E29" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" thickBot="1">
@@ -3248,19 +3516,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>69</v>
-      </c>
       <c r="E30" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" thickBot="1">
@@ -3268,19 +3536,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>71</v>
-      </c>
       <c r="E31" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" thickBot="1">
@@ -3288,19 +3556,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D32" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>73</v>
-      </c>
       <c r="E32" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15" thickBot="1">
@@ -3308,19 +3576,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>75</v>
-      </c>
       <c r="E33" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15" thickBot="1">
@@ -3328,19 +3596,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>77</v>
-      </c>
       <c r="E34" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" thickBot="1">
@@ -3348,19 +3616,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D35" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="C35" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>79</v>
-      </c>
       <c r="E35" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15" thickBot="1">
@@ -3368,19 +3636,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="D36" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="E36" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15" thickBot="1">
@@ -3388,19 +3656,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>84</v>
-      </c>
       <c r="E37" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" thickBot="1">
@@ -3408,19 +3676,19 @@
         <v>37</v>
       </c>
       <c r="B38" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D38" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C38" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>86</v>
-      </c>
       <c r="E38" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" thickBot="1">
@@ -3428,19 +3696,19 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D39" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>88</v>
-      </c>
       <c r="E39" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15" thickBot="1">
@@ -3448,19 +3716,19 @@
         <v>39</v>
       </c>
       <c r="B40" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>90</v>
-      </c>
       <c r="E40" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15" thickBot="1">
@@ -3468,19 +3736,19 @@
         <v>40</v>
       </c>
       <c r="B41" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D41" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>92</v>
-      </c>
       <c r="E41" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15" thickBot="1">
@@ -3488,19 +3756,19 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D42" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>94</v>
-      </c>
       <c r="E42" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" thickBot="1">
@@ -3508,19 +3776,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D43" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>96</v>
-      </c>
       <c r="E43" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15" thickBot="1">
@@ -3528,19 +3796,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D44" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>98</v>
-      </c>
       <c r="E44" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15" thickBot="1">
@@ -3548,19 +3816,19 @@
         <v>44</v>
       </c>
       <c r="B45" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D45" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="C45" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>100</v>
-      </c>
       <c r="E45" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" thickBot="1">
@@ -3568,19 +3836,19 @@
         <v>45</v>
       </c>
       <c r="B46" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D46" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C46" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>102</v>
-      </c>
       <c r="E46" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15" thickBot="1">
@@ -3588,19 +3856,19 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="D47" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D47" s="5" t="s">
-        <v>105</v>
-      </c>
       <c r="E47" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15" thickBot="1">
@@ -3608,19 +3876,19 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D48" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C48" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>107</v>
-      </c>
       <c r="E48" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15" thickBot="1">
@@ -3628,19 +3896,19 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D49" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>109</v>
-      </c>
       <c r="E49" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15" thickBot="1">
@@ -3648,19 +3916,19 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D50" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C50" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="E50" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15" thickBot="1">
@@ -3668,19 +3936,19 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D51" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C51" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>113</v>
-      </c>
       <c r="E51" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15" thickBot="1">
@@ -3688,19 +3956,19 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D52" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C52" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>115</v>
-      </c>
       <c r="E52" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15" thickBot="1">
@@ -3708,19 +3976,19 @@
         <v>52</v>
       </c>
       <c r="B53" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D53" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="C53" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>117</v>
-      </c>
       <c r="E53" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15" thickBot="1">
@@ -3728,19 +3996,19 @@
         <v>53</v>
       </c>
       <c r="B54" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D54" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>119</v>
-      </c>
       <c r="E54" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15" thickBot="1">
@@ -3748,19 +4016,19 @@
         <v>54</v>
       </c>
       <c r="B55" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D55" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C55" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>121</v>
-      </c>
       <c r="E55" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15" thickBot="1">
@@ -3768,19 +4036,19 @@
         <v>55</v>
       </c>
       <c r="B56" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D56" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="C56" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>123</v>
-      </c>
       <c r="E56" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" thickBot="1">
@@ -3788,19 +4056,19 @@
         <v>56</v>
       </c>
       <c r="B57" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D57" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C57" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>125</v>
-      </c>
       <c r="E57" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15" thickBot="1">
@@ -3808,19 +4076,19 @@
         <v>57</v>
       </c>
       <c r="B58" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D58" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C58" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>127</v>
-      </c>
       <c r="E58" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15" thickBot="1">
@@ -3828,19 +4096,19 @@
         <v>58</v>
       </c>
       <c r="B59" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D59" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="C59" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>129</v>
-      </c>
       <c r="E59" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15" thickBot="1">
@@ -3848,19 +4116,19 @@
         <v>59</v>
       </c>
       <c r="B60" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D60" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="C60" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D60" s="10" t="s">
-        <v>131</v>
-      </c>
       <c r="E60" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15" thickBot="1">
@@ -3868,19 +4136,19 @@
         <v>60</v>
       </c>
       <c r="B61" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D61" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="C61" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D61" s="10" t="s">
-        <v>133</v>
-      </c>
       <c r="E61" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15" thickBot="1">
@@ -3888,19 +4156,19 @@
         <v>61</v>
       </c>
       <c r="B62" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C62" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="D62" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="D62" s="7" t="s">
-        <v>136</v>
-      </c>
       <c r="E62" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15" thickBot="1">
@@ -3908,19 +4176,19 @@
         <v>62</v>
       </c>
       <c r="B63" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D63" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C63" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>138</v>
-      </c>
       <c r="E63" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15" thickBot="1">
@@ -3928,19 +4196,19 @@
         <v>63</v>
       </c>
       <c r="B64" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="D64" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="C64" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="D64" s="10" t="s">
-        <v>140</v>
-      </c>
       <c r="E64" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15" thickBot="1">
@@ -3948,19 +4216,19 @@
         <v>64</v>
       </c>
       <c r="B65" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C65" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="D65" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D65" s="5" t="s">
-        <v>143</v>
-      </c>
       <c r="E65" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" thickBot="1">
@@ -3968,19 +4236,19 @@
         <v>65</v>
       </c>
       <c r="B66" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D66" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C66" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>145</v>
-      </c>
       <c r="E66" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" thickBot="1">
@@ -3988,19 +4256,19 @@
         <v>66</v>
       </c>
       <c r="B67" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D67" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C67" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>147</v>
-      </c>
       <c r="E67" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15" thickBot="1">
@@ -4008,19 +4276,19 @@
         <v>67</v>
       </c>
       <c r="B68" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D68" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="C68" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>149</v>
-      </c>
       <c r="E68" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" thickBot="1">
@@ -4028,19 +4296,19 @@
         <v>68</v>
       </c>
       <c r="B69" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D69" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C69" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>151</v>
-      </c>
       <c r="E69" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15" thickBot="1">
@@ -4048,19 +4316,19 @@
         <v>69</v>
       </c>
       <c r="B70" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D70" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="C70" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>153</v>
-      </c>
       <c r="E70" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15" thickBot="1">
@@ -4068,22 +4336,22 @@
         <v>70</v>
       </c>
       <c r="B71" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="D71" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="C71" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="D71" s="10" t="s">
-        <v>155</v>
-      </c>
       <c r="E71" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G71" s="26" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15" thickBot="1">
@@ -4091,22 +4359,22 @@
         <v>71</v>
       </c>
       <c r="B72" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C72" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="C72" s="6" t="s">
+      <c r="D72" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D72" s="7" t="s">
-        <v>158</v>
-      </c>
       <c r="E72" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G72" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15" thickBot="1">
@@ -4114,19 +4382,19 @@
         <v>72</v>
       </c>
       <c r="B73" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D73" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C73" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>160</v>
-      </c>
       <c r="E73" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15" thickBot="1">
@@ -4134,19 +4402,19 @@
         <v>73</v>
       </c>
       <c r="B74" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D74" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C74" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>162</v>
-      </c>
       <c r="E74" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15" thickBot="1">
@@ -4154,19 +4422,19 @@
         <v>74</v>
       </c>
       <c r="B75" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D75" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="C75" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>164</v>
-      </c>
       <c r="E75" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15" thickBot="1">
@@ -4174,19 +4442,19 @@
         <v>75</v>
       </c>
       <c r="B76" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D76" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C76" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="E76" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15" thickBot="1">
@@ -4194,19 +4462,19 @@
         <v>76</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15" thickBot="1">
@@ -4214,19 +4482,19 @@
         <v>77</v>
       </c>
       <c r="B78" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D78" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="C78" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>169</v>
-      </c>
       <c r="E78" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" thickBot="1">
@@ -4234,646 +4502,719 @@
         <v>78</v>
       </c>
       <c r="B79" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D79" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="C79" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>171</v>
-      </c>
       <c r="E79" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F79" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="80" spans="1:7" ht="15" thickBot="1">
       <c r="A80" s="9">
         <v>79</v>
       </c>
       <c r="B80" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D80" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="C80" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="D80" s="10" t="s">
-        <v>173</v>
-      </c>
       <c r="E80" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F80" s="9"/>
-    </row>
-    <row r="81" spans="1:6" ht="15" thickBot="1">
+        <v>36</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="15" thickBot="1">
       <c r="A81" s="6">
         <v>80</v>
       </c>
       <c r="B81" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C81" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="C81" s="6" t="s">
+      <c r="D81" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="D81" s="7" t="s">
-        <v>176</v>
-      </c>
       <c r="E81" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F81" s="6"/>
-    </row>
-    <row r="82" spans="1:6" ht="15" thickBot="1">
+        <v>14</v>
+      </c>
+      <c r="F81" s="6" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="15" thickBot="1">
       <c r="A82" s="6">
         <v>81</v>
       </c>
       <c r="B82" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D82" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C82" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>178</v>
-      </c>
       <c r="E82" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F82" s="6"/>
-    </row>
-    <row r="83" spans="1:6" ht="15" thickBot="1">
+        <v>14</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="15" thickBot="1">
       <c r="A83" s="6">
         <v>82</v>
       </c>
       <c r="B83" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D83" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="C83" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>180</v>
-      </c>
       <c r="E83" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F83" s="6"/>
-    </row>
-    <row r="84" spans="1:6" ht="15" thickBot="1">
+        <v>14</v>
+      </c>
+      <c r="F83" s="6" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="15" thickBot="1">
       <c r="A84" s="6">
         <v>83</v>
       </c>
       <c r="B84" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D84" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="C84" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>182</v>
-      </c>
       <c r="E84" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F84" s="6"/>
-    </row>
-    <row r="85" spans="1:6" ht="15" thickBot="1">
+        <v>14</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="15" thickBot="1">
       <c r="A85" s="6">
         <v>84</v>
       </c>
       <c r="B85" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D85" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="C85" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>184</v>
-      </c>
       <c r="E85" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F85" s="6"/>
-    </row>
-    <row r="86" spans="1:6" ht="15" thickBot="1">
+        <v>14</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="15" thickBot="1">
       <c r="A86" s="6">
         <v>85</v>
       </c>
       <c r="B86" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D86" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="C86" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>186</v>
-      </c>
       <c r="E86" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F86" s="6"/>
-    </row>
-    <row r="87" spans="1:6" ht="15" thickBot="1">
+        <v>14</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="15" thickBot="1">
       <c r="A87" s="6">
         <v>86</v>
       </c>
       <c r="B87" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D87" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C87" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>188</v>
-      </c>
       <c r="E87" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F87" s="6"/>
-    </row>
-    <row r="88" spans="1:6" ht="15" thickBot="1">
+        <v>14</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="15" thickBot="1">
       <c r="A88" s="6">
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D88" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="C88" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>190</v>
-      </c>
       <c r="E88" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F88" s="6"/>
-    </row>
-    <row r="89" spans="1:6" ht="15" thickBot="1">
+        <v>14</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="15" thickBot="1">
       <c r="A89" s="6">
         <v>88</v>
       </c>
       <c r="B89" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D89" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="C89" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>192</v>
-      </c>
       <c r="E89" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F89" s="6"/>
-    </row>
-    <row r="90" spans="1:6" ht="15" thickBot="1">
+        <v>14</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="15" thickBot="1">
       <c r="A90" s="6">
         <v>89</v>
       </c>
       <c r="B90" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D90" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="C90" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>194</v>
-      </c>
       <c r="E90" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F90" s="6"/>
-    </row>
-    <row r="91" spans="1:6" ht="15" thickBot="1">
+        <v>14</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="15" thickBot="1">
       <c r="A91" s="6">
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D91" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="C91" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D91" s="7" t="s">
-        <v>196</v>
-      </c>
       <c r="E91" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F91" s="6"/>
-    </row>
-    <row r="92" spans="1:6" ht="15" thickBot="1">
+        <v>14</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="15" thickBot="1">
       <c r="A92" s="6">
         <v>91</v>
       </c>
       <c r="B92" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D92" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="C92" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D92" s="7" t="s">
-        <v>198</v>
-      </c>
       <c r="E92" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F92" s="6"/>
-    </row>
-    <row r="93" spans="1:6" ht="15" thickBot="1">
+        <v>14</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="15" thickBot="1">
       <c r="A93" s="9">
         <v>92</v>
       </c>
       <c r="B93" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="D93" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="C93" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="D93" s="10" t="s">
-        <v>200</v>
-      </c>
       <c r="E93" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F93" s="9"/>
-    </row>
-    <row r="94" spans="1:6" ht="15" thickBot="1">
+        <v>36</v>
+      </c>
+      <c r="F93" s="9" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="15" thickBot="1">
       <c r="A94" s="9">
         <v>93</v>
       </c>
       <c r="B94" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C94" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="C94" s="9" t="s">
+      <c r="D94" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="D94" s="10" t="s">
-        <v>203</v>
-      </c>
       <c r="E94" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F94" s="9"/>
-    </row>
-    <row r="95" spans="1:6" ht="15" thickBot="1">
+        <v>36</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="15" thickBot="1">
       <c r="A95" s="6">
         <v>94</v>
       </c>
       <c r="B95" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D95" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C95" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>205</v>
-      </c>
       <c r="E95" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F95" s="6"/>
-    </row>
-    <row r="96" spans="1:6" ht="15" thickBot="1">
+        <v>14</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="G95" s="27" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="15" thickBot="1">
       <c r="A96" s="6">
         <v>95</v>
       </c>
       <c r="B96" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D96" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="C96" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="D96" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="E96" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F96" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="97" spans="1:6" ht="15" thickBot="1">
       <c r="A97" s="9">
         <v>96</v>
       </c>
       <c r="B97" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="D97" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="C97" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="D97" s="10" t="s">
-        <v>209</v>
-      </c>
       <c r="E97" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F97" s="9"/>
+        <v>36</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="98" spans="1:6" ht="15" thickBot="1">
       <c r="A98" s="9">
         <v>97</v>
       </c>
       <c r="B98" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="D98" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="C98" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="D98" s="10" t="s">
-        <v>211</v>
-      </c>
       <c r="E98" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F98" s="9"/>
+        <v>36</v>
+      </c>
+      <c r="F98" s="9" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="99" spans="1:6" ht="15" thickBot="1">
       <c r="A99" s="6">
         <v>98</v>
       </c>
       <c r="B99" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D99" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="C99" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="D99" s="7" t="s">
-        <v>213</v>
-      </c>
       <c r="E99" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F99" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="100" spans="1:6" ht="15" thickBot="1">
       <c r="A100" s="4">
         <v>99</v>
       </c>
       <c r="B100" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C100" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="D100" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="D100" s="5" t="s">
-        <v>216</v>
-      </c>
       <c r="E100" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F100" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="101" spans="1:6" ht="15" thickBot="1">
       <c r="A101" s="4">
         <v>100</v>
       </c>
       <c r="B101" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D101" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="C101" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D101" s="5" t="s">
-        <v>218</v>
-      </c>
       <c r="E101" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F101" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="102" spans="1:6" ht="15" thickBot="1">
       <c r="A102" s="6">
         <v>101</v>
       </c>
       <c r="B102" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D102" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="C102" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="D102" s="7" t="s">
-        <v>220</v>
-      </c>
       <c r="E102" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F102" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="103" spans="1:6" ht="15" thickBot="1">
       <c r="A103" s="6">
         <v>102</v>
       </c>
       <c r="B103" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D103" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="C103" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>222</v>
-      </c>
       <c r="E103" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F103" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="104" spans="1:6" ht="15" thickBot="1">
       <c r="A104" s="6">
         <v>103</v>
       </c>
       <c r="B104" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D104" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="C104" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>224</v>
-      </c>
       <c r="E104" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F104" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="105" spans="1:6" ht="15" thickBot="1">
       <c r="A105" s="6">
         <v>104</v>
       </c>
       <c r="B105" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D105" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="C105" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>226</v>
-      </c>
       <c r="E105" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F105" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="106" spans="1:6" ht="15" thickBot="1">
       <c r="A106" s="6">
         <v>105</v>
       </c>
       <c r="B106" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D106" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="C106" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="D106" s="7" t="s">
-        <v>228</v>
-      </c>
       <c r="E106" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F106" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="107" spans="1:6" ht="15" thickBot="1">
       <c r="A107" s="6">
         <v>106</v>
       </c>
       <c r="B107" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D107" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="C107" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="D107" s="7" t="s">
-        <v>230</v>
-      </c>
       <c r="E107" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F107" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="F107" s="6" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="108" spans="1:6" ht="15" thickBot="1">
       <c r="A108" s="6">
         <v>107</v>
       </c>
       <c r="B108" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D108" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="C108" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="D108" s="7" t="s">
-        <v>232</v>
-      </c>
       <c r="E108" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F108" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="109" spans="1:6" ht="15" thickBot="1">
       <c r="A109" s="6">
         <v>108</v>
       </c>
       <c r="B109" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D109" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="C109" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="D109" s="7" t="s">
-        <v>234</v>
-      </c>
       <c r="E109" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F109" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="110" spans="1:6" ht="15" thickBot="1">
       <c r="A110" s="6">
         <v>109</v>
       </c>
       <c r="B110" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D110" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="C110" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="D110" s="7" t="s">
-        <v>236</v>
-      </c>
       <c r="E110" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F110" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="111" spans="1:6" ht="15" thickBot="1">
       <c r="A111" s="6">
         <v>110</v>
       </c>
       <c r="B111" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D111" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="C111" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="D111" s="7" t="s">
-        <v>238</v>
-      </c>
       <c r="E111" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F111" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="F111" s="6" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="112" spans="1:6" ht="15" thickBot="1">
       <c r="A112" s="6">
         <v>111</v>
       </c>
       <c r="B112" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="C112" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="C112" s="6" t="s">
+      <c r="D112" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="D112" s="7" t="s">
-        <v>241</v>
-      </c>
       <c r="E112" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F112" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="F112" s="6" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="113" spans="1:6" ht="15" thickBot="1">
       <c r="A113" s="6">
         <v>112</v>
       </c>
       <c r="B113" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="D113" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="C113" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="D113" s="7" t="s">
-        <v>243</v>
-      </c>
       <c r="E113" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F113" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="F113" s="6" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="114" spans="1:6" ht="15" thickBot="1">
       <c r="A114" s="6">
         <v>113</v>
       </c>
       <c r="B114" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="D114" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="C114" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="D114" s="7" t="s">
-        <v>245</v>
-      </c>
       <c r="E114" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F114" s="6"/>
     </row>
@@ -4882,16 +5223,16 @@
         <v>114</v>
       </c>
       <c r="B115" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="D115" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="C115" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="D115" s="7" t="s">
-        <v>247</v>
-      </c>
       <c r="E115" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F115" s="6"/>
     </row>
@@ -4900,16 +5241,16 @@
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="D116" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="C116" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="D116" s="7" t="s">
-        <v>249</v>
-      </c>
       <c r="E116" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F116" s="6"/>
     </row>
@@ -4918,16 +5259,16 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="D117" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="C117" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="D117" s="7" t="s">
-        <v>251</v>
-      </c>
       <c r="E117" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F117" s="6"/>
     </row>
@@ -4936,16 +5277,16 @@
         <v>117</v>
       </c>
       <c r="B118" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="C118" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D118" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="C118" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="D118" s="10" t="s">
-        <v>253</v>
-      </c>
       <c r="E118" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F118" s="9"/>
     </row>
@@ -4954,16 +5295,16 @@
         <v>118</v>
       </c>
       <c r="B119" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C119" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D119" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="C119" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="D119" s="10" t="s">
-        <v>255</v>
-      </c>
       <c r="E119" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F119" s="9"/>
     </row>
@@ -4972,16 +5313,16 @@
         <v>119</v>
       </c>
       <c r="B120" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="D120" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="C120" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="D120" s="7" t="s">
-        <v>257</v>
-      </c>
       <c r="E120" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F120" s="6"/>
     </row>
@@ -4990,16 +5331,16 @@
         <v>120</v>
       </c>
       <c r="B121" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="C121" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D121" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="C121" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="D121" s="10" t="s">
-        <v>259</v>
-      </c>
       <c r="E121" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F121" s="9"/>
     </row>
@@ -5008,16 +5349,16 @@
         <v>121</v>
       </c>
       <c r="B122" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="C122" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D122" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="C122" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="D122" s="10" t="s">
-        <v>261</v>
-      </c>
       <c r="E122" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F122" s="9"/>
     </row>
@@ -5026,16 +5367,16 @@
         <v>122</v>
       </c>
       <c r="B123" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C123" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="C123" s="6" t="s">
+      <c r="D123" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="D123" s="7" t="s">
-        <v>264</v>
-      </c>
       <c r="E123" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F123" s="6"/>
     </row>
@@ -5044,16 +5385,16 @@
         <v>123</v>
       </c>
       <c r="B124" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="D124" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="C124" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="D124" s="7" t="s">
-        <v>266</v>
-      </c>
       <c r="E124" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F124" s="6"/>
     </row>
@@ -5062,16 +5403,16 @@
         <v>124</v>
       </c>
       <c r="B125" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="D125" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="C125" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="D125" s="7" t="s">
-        <v>268</v>
-      </c>
       <c r="E125" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F125" s="6"/>
     </row>
@@ -5080,16 +5421,16 @@
         <v>125</v>
       </c>
       <c r="B126" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="D126" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="C126" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="D126" s="7" t="s">
-        <v>270</v>
-      </c>
       <c r="E126" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F126" s="6"/>
     </row>
@@ -5098,16 +5439,16 @@
         <v>126</v>
       </c>
       <c r="B127" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="D127" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="C127" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="D127" s="7" t="s">
-        <v>272</v>
-      </c>
       <c r="E127" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F127" s="6"/>
     </row>
@@ -5116,16 +5457,16 @@
         <v>127</v>
       </c>
       <c r="B128" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="D128" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="C128" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="D128" s="7" t="s">
-        <v>274</v>
-      </c>
       <c r="E128" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F128" s="6"/>
     </row>
@@ -5134,16 +5475,16 @@
         <v>128</v>
       </c>
       <c r="B129" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="D129" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="C129" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="D129" s="7" t="s">
-        <v>276</v>
-      </c>
       <c r="E129" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F129" s="6"/>
     </row>
@@ -5152,16 +5493,16 @@
         <v>129</v>
       </c>
       <c r="B130" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="D130" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="C130" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="D130" s="7" t="s">
-        <v>278</v>
-      </c>
       <c r="E130" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F130" s="6"/>
     </row>
@@ -5170,16 +5511,16 @@
         <v>130</v>
       </c>
       <c r="B131" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="C131" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="C131" s="6" t="s">
+      <c r="D131" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="D131" s="7" t="s">
-        <v>281</v>
-      </c>
       <c r="E131" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F131" s="6"/>
     </row>
@@ -5188,16 +5529,16 @@
         <v>131</v>
       </c>
       <c r="B132" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="D132" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="C132" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="D132" s="7" t="s">
-        <v>283</v>
-      </c>
       <c r="E132" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F132" s="6"/>
     </row>
@@ -5206,16 +5547,16 @@
         <v>132</v>
       </c>
       <c r="B133" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="D133" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="C133" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="D133" s="7" t="s">
-        <v>285</v>
-      </c>
       <c r="E133" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F133" s="6"/>
     </row>
@@ -5224,16 +5565,16 @@
         <v>133</v>
       </c>
       <c r="B134" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="D134" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="C134" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="D134" s="5" t="s">
-        <v>287</v>
-      </c>
       <c r="E134" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F134" s="4"/>
     </row>
@@ -5242,16 +5583,16 @@
         <v>134</v>
       </c>
       <c r="B135" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="D135" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="C135" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="D135" s="7" t="s">
-        <v>289</v>
-      </c>
       <c r="E135" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F135" s="6"/>
     </row>
@@ -5260,16 +5601,16 @@
         <v>135</v>
       </c>
       <c r="B136" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="C136" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="D136" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="C136" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="D136" s="10" t="s">
-        <v>291</v>
-      </c>
       <c r="E136" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F136" s="9"/>
     </row>
@@ -5278,16 +5619,16 @@
         <v>136</v>
       </c>
       <c r="B137" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="C137" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="C137" s="6" t="s">
+      <c r="D137" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="D137" s="7" t="s">
-        <v>294</v>
-      </c>
       <c r="E137" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F137" s="6"/>
     </row>
@@ -5296,16 +5637,16 @@
         <v>137</v>
       </c>
       <c r="B138" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="D138" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="C138" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="D138" s="7" t="s">
-        <v>296</v>
-      </c>
       <c r="E138" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F138" s="6"/>
     </row>
@@ -5314,16 +5655,16 @@
         <v>138</v>
       </c>
       <c r="B139" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="D139" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="C139" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="D139" s="7" t="s">
-        <v>298</v>
-      </c>
       <c r="E139" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F139" s="6"/>
     </row>
@@ -5332,16 +5673,16 @@
         <v>139</v>
       </c>
       <c r="B140" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="D140" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="C140" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="D140" s="5" t="s">
-        <v>300</v>
-      </c>
       <c r="E140" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F140" s="4"/>
     </row>
@@ -5350,16 +5691,16 @@
         <v>140</v>
       </c>
       <c r="B141" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="D141" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="C141" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="D141" s="5" t="s">
-        <v>302</v>
-      </c>
       <c r="E141" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F141" s="4"/>
     </row>
@@ -5368,16 +5709,16 @@
         <v>141</v>
       </c>
       <c r="B142" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="D142" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="C142" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="D142" s="7" t="s">
-        <v>304</v>
-      </c>
       <c r="E142" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F142" s="6"/>
     </row>
@@ -5386,16 +5727,16 @@
         <v>142</v>
       </c>
       <c r="B143" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="D143" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="C143" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="D143" s="7" t="s">
-        <v>306</v>
-      </c>
       <c r="E143" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F143" s="6"/>
     </row>
@@ -5404,16 +5745,16 @@
         <v>143</v>
       </c>
       <c r="B144" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="D144" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="C144" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="D144" s="7" t="s">
-        <v>308</v>
-      </c>
       <c r="E144" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F144" s="6"/>
     </row>
@@ -5422,16 +5763,16 @@
         <v>144</v>
       </c>
       <c r="B145" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C145" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="C145" s="4" t="s">
+      <c r="D145" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="D145" s="5" t="s">
-        <v>311</v>
-      </c>
       <c r="E145" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F145" s="4"/>
     </row>
@@ -5440,16 +5781,16 @@
         <v>145</v>
       </c>
       <c r="B146" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="D146" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="C146" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="D146" s="5" t="s">
-        <v>313</v>
-      </c>
       <c r="E146" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F146" s="4"/>
     </row>
@@ -5458,16 +5799,16 @@
         <v>146</v>
       </c>
       <c r="B147" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="D147" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="C147" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="D147" s="5" t="s">
-        <v>315</v>
-      </c>
       <c r="E147" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F147" s="4"/>
     </row>
@@ -5476,16 +5817,16 @@
         <v>147</v>
       </c>
       <c r="B148" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="D148" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="C148" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="D148" s="5" t="s">
-        <v>317</v>
-      </c>
       <c r="E148" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F148" s="4"/>
     </row>
@@ -5494,16 +5835,16 @@
         <v>148</v>
       </c>
       <c r="B149" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="D149" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="C149" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="D149" s="5" t="s">
-        <v>319</v>
-      </c>
       <c r="E149" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F149" s="4"/>
     </row>
@@ -5512,16 +5853,16 @@
         <v>149</v>
       </c>
       <c r="B150" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="D150" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="C150" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="D150" s="7" t="s">
-        <v>321</v>
-      </c>
       <c r="E150" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F150" s="6"/>
     </row>
@@ -5530,109 +5871,144 @@
         <v>150</v>
       </c>
       <c r="B151" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="D151" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="C151" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="D151" s="7" t="s">
-        <v>323</v>
-      </c>
       <c r="E151" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F151" s="6"/>
     </row>
     <row r="155" spans="1:6">
       <c r="C155" s="21" t="s">
+        <v>608</v>
+      </c>
+      <c r="D155" s="21" t="s">
         <v>609</v>
       </c>
-      <c r="D155" s="21" t="s">
+      <c r="E155" s="21" t="s">
         <v>610</v>
       </c>
-      <c r="E155" s="21" t="s">
+      <c r="F155" s="21" t="s">
         <v>611</v>
-      </c>
-      <c r="F155" s="21" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="C156" s="21" t="s">
+        <v>612</v>
+      </c>
+      <c r="D156" s="22" t="s">
         <v>613</v>
       </c>
-      <c r="D156" s="22" t="s">
-        <v>614</v>
-      </c>
       <c r="E156" s="21" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="40.799999999999997">
       <c r="D157" s="23" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E157" s="21" t="s">
+        <v>619</v>
+      </c>
+      <c r="F157" s="21" t="s">
         <v>620</v>
-      </c>
-      <c r="F157" s="21" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="D158" s="22" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="159" spans="1:6">
       <c r="C159" s="25" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D159" s="24" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="D160" s="23" t="s">
-        <v>618</v>
+        <v>617</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" s="28" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="28" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" s="28" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="28" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" s="28" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" s="28" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="180" spans="3:12" ht="15" thickBot="1"/>
     <row r="181" spans="3:12" ht="28.2" thickBot="1">
       <c r="C181" s="18" t="s">
+        <v>554</v>
+      </c>
+      <c r="D181" s="18" t="s">
         <v>555</v>
       </c>
-      <c r="D181" s="18" t="s">
+      <c r="E181" s="18" t="s">
         <v>556</v>
       </c>
-      <c r="E181" s="18" t="s">
+      <c r="F181" s="18" t="s">
         <v>557</v>
       </c>
-      <c r="F181" s="18" t="s">
+      <c r="G181" s="18" t="s">
         <v>558</v>
       </c>
-      <c r="G181" s="18" t="s">
+      <c r="H181" s="18" t="s">
         <v>559</v>
       </c>
-      <c r="H181" s="18" t="s">
+      <c r="I181" s="18" t="s">
         <v>560</v>
       </c>
-      <c r="I181" s="18" t="s">
+      <c r="J181" s="18" t="s">
         <v>561</v>
       </c>
-      <c r="J181" s="18" t="s">
+      <c r="K181" s="18" t="s">
         <v>562</v>
       </c>
-      <c r="K181" s="18" t="s">
+      <c r="L181" s="18" t="s">
         <v>563</v>
-      </c>
-      <c r="L181" s="18" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="182" spans="3:12" ht="15" thickBot="1">
       <c r="C182" s="18" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D182" s="19">
         <v>4</v>
@@ -5659,12 +6035,12 @@
         <v>33</v>
       </c>
       <c r="L182" s="19" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="183" spans="3:12" ht="28.2" thickBot="1">
       <c r="C183" s="18" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D183" s="19">
         <v>4</v>
@@ -5691,12 +6067,12 @@
         <v>36</v>
       </c>
       <c r="L183" s="19" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="184" spans="3:12" ht="28.2" thickBot="1">
       <c r="C184" s="18" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D184" s="19">
         <v>3</v>
@@ -5723,12 +6099,12 @@
         <v>27</v>
       </c>
       <c r="L184" s="19" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="185" spans="3:12" ht="42" thickBot="1">
       <c r="C185" s="18" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D185" s="19">
         <v>5</v>
@@ -5755,12 +6131,12 @@
         <v>25</v>
       </c>
       <c r="L185" s="19" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="186" spans="3:12" ht="42" thickBot="1">
       <c r="C186" s="18" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D186" s="19">
         <v>3</v>
@@ -5787,12 +6163,12 @@
         <v>25</v>
       </c>
       <c r="L186" s="19" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="187" spans="3:12" ht="15" thickBot="1">
       <c r="C187" s="18" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D187" s="19">
         <v>3</v>
@@ -5819,12 +6195,12 @@
         <v>22</v>
       </c>
       <c r="L187" s="19" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="188" spans="3:12" ht="42" thickBot="1">
       <c r="C188" s="18" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D188" s="19">
         <v>3</v>
@@ -5851,12 +6227,12 @@
         <v>26</v>
       </c>
       <c r="L188" s="19" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="189" spans="3:12" ht="15" thickBot="1">
       <c r="C189" s="18" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D189" s="19">
         <v>3</v>
@@ -5883,12 +6259,12 @@
         <v>30</v>
       </c>
       <c r="L189" s="19" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="190" spans="3:12" ht="42" thickBot="1">
       <c r="C190" s="18" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D190" s="19">
         <v>4</v>
@@ -5915,12 +6291,12 @@
         <v>29</v>
       </c>
       <c r="L190" s="19" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="191" spans="3:12" ht="42" thickBot="1">
       <c r="C191" s="18" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D191" s="19">
         <v>5</v>
@@ -5947,12 +6323,12 @@
         <v>26</v>
       </c>
       <c r="L191" s="19" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="192" spans="3:12" ht="42" thickBot="1">
       <c r="C192" s="18" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D192" s="19">
         <v>4</v>
@@ -5979,12 +6355,12 @@
         <v>26</v>
       </c>
       <c r="L192" s="19" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="193" spans="3:12" ht="15" thickBot="1">
       <c r="C193" s="18" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D193" s="19">
         <v>7</v>
@@ -6011,12 +6387,12 @@
         <v>32</v>
       </c>
       <c r="L193" s="19" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="194" spans="3:12" ht="15" thickBot="1">
       <c r="C194" s="18" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D194" s="18">
         <v>48</v>
@@ -6043,33 +6419,33 @@
         <v>337</v>
       </c>
       <c r="L194" s="19" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="195" spans="3:12" ht="15" thickBot="1"/>
     <row r="196" spans="3:12" ht="42" thickBot="1">
       <c r="C196" s="18" t="s">
+        <v>584</v>
+      </c>
+      <c r="D196" s="18" t="s">
         <v>585</v>
       </c>
-      <c r="D196" s="18" t="s">
+      <c r="E196" s="18" t="s">
         <v>586</v>
       </c>
-      <c r="E196" s="18" t="s">
+      <c r="F196" s="18" t="s">
         <v>587</v>
       </c>
-      <c r="F196" s="18" t="s">
+      <c r="G196" s="18" t="s">
         <v>588</v>
-      </c>
-      <c r="G196" s="18" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="197" spans="3:12" ht="152.4" thickBot="1">
       <c r="C197" s="18" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D197" s="18" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E197" s="20">
         <v>46239</v>
@@ -6078,15 +6454,15 @@
         <v>25</v>
       </c>
       <c r="G197" s="19" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="198" spans="3:12" ht="124.8" thickBot="1">
       <c r="C198" s="18" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D198" s="18" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E198" s="20">
         <v>46238</v>
@@ -6095,15 +6471,15 @@
         <v>25</v>
       </c>
       <c r="G198" s="19" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="199" spans="3:12" ht="152.4" thickBot="1">
       <c r="C199" s="18" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D199" s="18" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E199" s="20">
         <v>46237</v>
@@ -6112,15 +6488,15 @@
         <v>25</v>
       </c>
       <c r="G199" s="19" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="200" spans="3:12" ht="180" thickBot="1">
       <c r="C200" s="18" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D200" s="18" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E200" s="20">
         <v>46240</v>
@@ -6129,15 +6505,15 @@
         <v>25</v>
       </c>
       <c r="G200" s="18" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="201" spans="3:12" ht="138.6" thickBot="1">
       <c r="C201" s="18" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D201" s="18" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E201" s="20">
         <v>46238</v>
@@ -6146,15 +6522,15 @@
         <v>26</v>
       </c>
       <c r="G201" s="19" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="202" spans="3:12" ht="152.4" thickBot="1">
       <c r="C202" s="18" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D202" s="18" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E202" s="20">
         <v>46238</v>
@@ -6163,15 +6539,15 @@
         <v>25</v>
       </c>
       <c r="G202" s="19" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="203" spans="3:12" ht="180" thickBot="1">
       <c r="C203" s="18" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D203" s="18" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E203" s="20">
         <v>46239</v>
@@ -6180,41 +6556,41 @@
         <v>27</v>
       </c>
       <c r="G203" s="19" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="204" spans="3:12" ht="180" thickBot="1">
       <c r="C204" s="18" t="s">
+        <v>602</v>
+      </c>
+      <c r="D204" s="18" t="s">
         <v>603</v>
       </c>
-      <c r="D204" s="18" t="s">
-        <v>604</v>
-      </c>
       <c r="E204" s="19" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F204" s="18">
         <v>36</v>
       </c>
       <c r="G204" s="19" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="205" spans="3:12" ht="152.4" thickBot="1">
       <c r="C205" s="18" t="s">
+        <v>605</v>
+      </c>
+      <c r="D205" s="18" t="s">
         <v>606</v>
       </c>
-      <c r="D205" s="18" t="s">
-        <v>607</v>
-      </c>
       <c r="E205" s="19" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F205" s="18">
         <v>30</v>
       </c>
       <c r="G205" s="19" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
   </sheetData>
@@ -6515,8 +6891,16 @@
     <hyperlink ref="D150" r:id="rId294" xr:uid="{79F588C1-D436-4FA8-8C8E-DECD14E9B249}"/>
     <hyperlink ref="B151" r:id="rId295" display="https://leetcode.com/problems/reverse-integer/" xr:uid="{B34C6A33-D2FE-4FC8-944C-70F568500B74}"/>
     <hyperlink ref="D151" r:id="rId296" xr:uid="{F66251C5-602C-4134-ACB4-79F6622D0056}"/>
+    <hyperlink ref="A164" r:id="rId297" display="https://leetcode.com/link/?target=https%3A%2F%2Fleetcode.com%2Fproblems%2Fcheapest-flights-within-k-stops%2F" xr:uid="{4C161C2D-0ED7-4651-9880-F7C7532A8973}"/>
+    <hyperlink ref="A165" r:id="rId298" display="https://leetcode.com/link/?target=https%3A%2F%2Fleetcode.com%2Fproblems%2Fswim-in-rising-water%2Fdescription%2F" xr:uid="{0505C84E-0F32-4AA9-B61E-63B4F9C626EE}"/>
+    <hyperlink ref="A166" r:id="rId299" display="https://leetcode.com/link/?target=https%3A%2F%2Fleetcode.com%2Fproblems%2Fbus-routes%2Fdescription%2F" xr:uid="{A75C5F39-47ED-4E64-8703-8C934880C859}"/>
+    <hyperlink ref="A167" r:id="rId300" display="https://leetcode.com/link/?target=https%3A%2F%2Fleetcode.com%2Fproblems%2Fshortest-path-in-binary-matrix%2Fdescription%2F" xr:uid="{FA710D28-22E1-48A9-A951-55B54D3BC354}"/>
+    <hyperlink ref="A168" r:id="rId301" display="https://leetcode.com/link/?target=https%3A%2F%2Fleetcode.com%2Fproblems%2Fpath-with-minimum-effort%2Fdescription%2F" xr:uid="{3E9431B2-68DD-4E84-B225-FA86E527E1EF}"/>
+    <hyperlink ref="A169" r:id="rId302" display="https://leetcode.com/link/?target=https%3A%2F%2Fleetcode.com%2Fproblems%2Ffind-the-safest-path-in-a-grid%2Fdescription%2F" xr:uid="{8E69E889-0964-4D73-906D-992669FE3D8E}"/>
+    <hyperlink ref="A170" r:id="rId303" display="https://leetcode.com/link/?target=https%3A%2F%2Fleetcode.com%2Fproblems%2Fdesign-graph-with-shortest-path-calculator%2Fdescription%2F" xr:uid="{C8D84BD1-2CCB-4250-A6C8-B8220946B10E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId304"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
@@ -6540,12 +6924,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4889946B-F73F-4F1F-B541-562830883ACD}">
-  <dimension ref="A2:N280"/>
+  <dimension ref="A2:O326"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="2" spans="1:2" ht="18">
       <c r="B2" s="13" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -6553,312 +6937,375 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="B9" s="14" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="B10" s="14" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="B11" s="14" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="B12" s="14" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="B13" s="14" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" s="14" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="B15" s="14" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="B16" s="14" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15">
+      <c r="B17" s="14" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="17" spans="2:14">
-      <c r="B17" s="14" t="s">
+    <row r="18" spans="2:15">
+      <c r="B18" s="14" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="18" spans="2:14">
-      <c r="B18" s="14" t="s">
+    <row r="19" spans="2:15">
+      <c r="B19" s="14" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="19" spans="2:14">
-      <c r="B19" s="14" t="s">
+    <row r="20" spans="2:15">
+      <c r="B20" s="14" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="20" spans="2:14">
-      <c r="B20" s="14" t="s">
+      <c r="N20" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15">
+      <c r="B21" s="14" t="s">
         <v>347</v>
       </c>
-      <c r="N20" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14">
-      <c r="B21" s="14" t="s">
+      <c r="N21" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15">
+      <c r="B22" s="14" t="s">
         <v>348</v>
       </c>
-      <c r="N21" t="s">
+      <c r="N22" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="22" spans="2:14">
-      <c r="B22" s="14" t="s">
+    <row r="23" spans="2:15">
+      <c r="B23" s="14" t="s">
         <v>349</v>
       </c>
-      <c r="N22" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="23" spans="2:14">
-      <c r="B23" s="14" t="s">
+    </row>
+    <row r="27" spans="2:15" ht="18">
+      <c r="B27" s="13" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="27" spans="2:14" ht="18">
-      <c r="B27" s="13" t="s">
+    <row r="28" spans="2:15" ht="28.8">
+      <c r="B28" s="14"/>
+      <c r="M28" s="30" t="s">
+        <v>685</v>
+      </c>
+      <c r="N28" s="30" t="s">
+        <v>686</v>
+      </c>
+      <c r="O28" s="30" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15">
+      <c r="B29" s="14" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="28" spans="2:14">
-      <c r="B28" s="14"/>
-    </row>
-    <row r="29" spans="2:14">
-      <c r="B29" s="14" t="s">
+      <c r="M29" s="31">
+        <v>1</v>
+      </c>
+      <c r="N29" s="31" t="s">
+        <v>680</v>
+      </c>
+      <c r="O29" s="31" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" ht="100.8">
+      <c r="B30" s="14" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="30" spans="2:14">
-      <c r="B30" s="14" t="s">
+      <c r="M30" s="31">
+        <v>2</v>
+      </c>
+      <c r="N30" s="31" t="s">
+        <v>681</v>
+      </c>
+      <c r="O30" s="31" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" ht="86.4">
+      <c r="B31" s="14" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="31" spans="2:14">
-      <c r="B31" s="14" t="s">
+      <c r="M31" s="31">
+        <v>3</v>
+      </c>
+      <c r="N31" s="31" t="s">
+        <v>682</v>
+      </c>
+      <c r="O31" s="31" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" ht="100.8">
+      <c r="B32" s="14" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="32" spans="2:14">
-      <c r="B32" s="14" t="s">
+      <c r="M32" s="31">
+        <v>4</v>
+      </c>
+      <c r="N32" s="31" t="s">
+        <v>683</v>
+      </c>
+      <c r="O32" s="31" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" ht="100.8">
+      <c r="B33" s="14" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="33" spans="2:2">
-      <c r="B33" s="14" t="s">
+      <c r="M33" s="31">
+        <v>5</v>
+      </c>
+      <c r="N33" s="31" t="s">
+        <v>684</v>
+      </c>
+      <c r="O33" s="31" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" ht="187.2">
+      <c r="B34" s="14" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="34" spans="2:2">
-      <c r="B34" s="14" t="s">
+      <c r="M34" s="31">
+        <v>6</v>
+      </c>
+      <c r="N34" s="31" t="s">
+        <v>693</v>
+      </c>
+      <c r="O34" s="31" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15">
+      <c r="B35" s="14" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="35" spans="2:2">
-      <c r="B35" s="14" t="s">
+    <row r="36" spans="2:15">
+      <c r="B36" s="14" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="36" spans="2:2">
-      <c r="B36" s="14" t="s">
+    <row r="37" spans="2:15">
+      <c r="B37" s="14" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="37" spans="2:2">
-      <c r="B37" s="14" t="s">
+    <row r="38" spans="2:15">
+      <c r="B38" s="14" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="38" spans="2:2">
-      <c r="B38" s="14" t="s">
+    <row r="39" spans="2:15">
+      <c r="B39" s="14" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="39" spans="2:2">
-      <c r="B39" s="14" t="s">
+    <row r="40" spans="2:15">
+      <c r="B40" s="14" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="40" spans="2:2">
-      <c r="B40" s="14" t="s">
+    <row r="41" spans="2:15">
+      <c r="B41" s="14" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="41" spans="2:2">
-      <c r="B41" s="14" t="s">
+    <row r="42" spans="2:15">
+      <c r="B42" s="14" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="42" spans="2:2">
-      <c r="B42" s="14" t="s">
+    <row r="43" spans="2:15">
+      <c r="B43" s="14" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="43" spans="2:2">
-      <c r="B43" s="14" t="s">
+    <row r="47" spans="2:15" ht="18">
+      <c r="B47" s="13" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="47" spans="2:2" ht="18">
-      <c r="B47" s="13" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="48" spans="2:2">
+    <row r="48" spans="2:15">
       <c r="B48" s="14"/>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" s="14" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" s="14" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" s="14" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" s="14" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="53" spans="2:2">
       <c r="B53" s="14" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" s="14" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="55" spans="2:2">
       <c r="B55" s="14" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" s="14" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" s="14" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="58" spans="2:2">
       <c r="B58" s="14" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="59" spans="2:2">
       <c r="B59" s="14" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" s="14" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" s="14" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" s="14" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63" s="14" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="64" spans="2:2">
       <c r="B64" s="14" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="65" spans="2:2">
       <c r="B65" s="14" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" s="14" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="70" spans="2:2" ht="18">
       <c r="B70" s="13" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="71" spans="2:2">
@@ -6866,87 +7313,87 @@
     </row>
     <row r="72" spans="2:2">
       <c r="B72" s="14" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="73" spans="2:2">
       <c r="B73" s="14" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="74" spans="2:2">
       <c r="B74" s="14" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" s="14" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="76" spans="2:2">
       <c r="B76" s="14" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="77" spans="2:2">
       <c r="B77" s="14" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78" s="14" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="79" spans="2:2">
       <c r="B79" s="14" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="80" spans="2:2">
       <c r="B80" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="81" spans="2:2">
       <c r="B81" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="82" spans="2:2">
       <c r="B82" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="83" spans="2:2">
       <c r="B83" s="14" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="84" spans="2:2">
       <c r="B84" s="14" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="85" spans="2:2">
       <c r="B85" s="14" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="86" spans="2:2">
       <c r="B86" s="14" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="87" spans="2:2">
       <c r="B87" s="14" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="91" spans="2:2" ht="18">
       <c r="B91" s="13" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="92" spans="2:2">
@@ -6954,107 +7401,107 @@
     </row>
     <row r="93" spans="2:2">
       <c r="B93" s="14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="94" spans="2:2">
       <c r="B94" s="14" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="95" spans="2:2">
       <c r="B95" s="14" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="96" spans="2:2">
       <c r="B96" s="14" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="97" spans="2:2">
       <c r="B97" s="14" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="98" spans="2:2">
       <c r="B98" s="14" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="99" spans="2:2">
       <c r="B99" s="14" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="100" spans="2:2">
       <c r="B100" s="14" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="101" spans="2:2">
       <c r="B101" s="14" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="102" spans="2:2">
       <c r="B102" s="14" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="103" spans="2:2">
       <c r="B103" s="14" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="104" spans="2:2">
       <c r="B104" s="14" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="105" spans="2:2">
       <c r="B105" s="14" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="106" spans="2:2">
       <c r="B106" s="14" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="107" spans="2:2">
       <c r="B107" s="14" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="108" spans="2:2">
       <c r="B108" s="14" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="109" spans="2:2">
       <c r="B109" s="14" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="110" spans="2:2">
       <c r="B110" s="14" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="111" spans="2:2">
       <c r="B111" s="14" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="112" spans="2:2">
       <c r="B112" s="14" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="116" spans="2:2" ht="18">
       <c r="B116" s="13" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="117" spans="2:2">
@@ -7062,82 +7509,82 @@
     </row>
     <row r="118" spans="2:2">
       <c r="B118" s="14" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="119" spans="2:2">
       <c r="B119" s="14" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="120" spans="2:2">
       <c r="B120" s="14" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="121" spans="2:2">
       <c r="B121" s="14" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="122" spans="2:2">
       <c r="B122" s="14" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="123" spans="2:2">
       <c r="B123" s="14" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="124" spans="2:2">
       <c r="B124" s="14" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="125" spans="2:2">
       <c r="B125" s="14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="126" spans="2:2">
       <c r="B126" s="14" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="127" spans="2:2">
       <c r="B127" s="14" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="128" spans="2:2">
       <c r="B128" s="14" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="129" spans="2:2">
       <c r="B129" s="14" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="130" spans="2:2">
       <c r="B130" s="14" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="131" spans="2:2">
       <c r="B131" s="14" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="132" spans="2:2">
       <c r="B132" s="14" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="136" spans="2:2" ht="18">
       <c r="B136" s="13" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="137" spans="2:2">
@@ -7145,67 +7592,67 @@
     </row>
     <row r="138" spans="2:2">
       <c r="B138" s="14" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="139" spans="2:2">
       <c r="B139" s="14" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="140" spans="2:2">
       <c r="B140" s="14" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="141" spans="2:2">
       <c r="B141" s="14" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="142" spans="2:2">
       <c r="B142" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="143" spans="2:2">
       <c r="B143" s="14" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="144" spans="2:2">
       <c r="B144" s="14" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="145" spans="2:2">
       <c r="B145" s="14" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="146" spans="2:2">
       <c r="B146" s="14" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="147" spans="2:2">
       <c r="B147" s="14" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="148" spans="2:2">
       <c r="B148" s="14" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="149" spans="2:2">
       <c r="B149" s="14" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="153" spans="2:2" ht="18">
       <c r="B153" s="13" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="154" spans="2:2">
@@ -7213,102 +7660,102 @@
     </row>
     <row r="155" spans="2:2">
       <c r="B155" s="14" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="156" spans="2:2">
       <c r="B156" s="14" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="157" spans="2:2">
       <c r="B157" s="14" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="158" spans="2:2">
       <c r="B158" s="14" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="159" spans="2:2">
       <c r="B159" s="14" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="160" spans="2:2">
       <c r="B160" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="161" spans="2:2">
       <c r="B161" s="14" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="162" spans="2:2">
       <c r="B162" s="14" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="163" spans="2:2">
       <c r="B163" s="14" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="164" spans="2:2">
       <c r="B164" s="14" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="165" spans="2:2">
       <c r="B165" s="14" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="166" spans="2:2">
       <c r="B166" s="14" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="167" spans="2:2">
       <c r="B167" s="14" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="168" spans="2:2">
       <c r="B168" s="14" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="169" spans="2:2">
       <c r="B169" s="14" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="170" spans="2:2">
       <c r="B170" s="14" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="171" spans="2:2">
       <c r="B171" s="14" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="172" spans="2:2">
       <c r="B172" s="14" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="173" spans="2:2">
       <c r="B173" s="14" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="177" spans="2:2" ht="18">
       <c r="B177" s="13" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="178" spans="2:2">
@@ -7316,42 +7763,42 @@
     </row>
     <row r="179" spans="2:2">
       <c r="B179" s="14" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="180" spans="2:2">
       <c r="B180" s="14" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="181" spans="2:2">
       <c r="B181" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="182" spans="2:2">
       <c r="B182" s="14" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="183" spans="2:2">
       <c r="B183" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="184" spans="2:2">
       <c r="B184" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="185" spans="2:2">
       <c r="B185" s="14" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="189" spans="2:2" ht="18">
       <c r="B189" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="190" spans="2:2">
@@ -7359,47 +7806,47 @@
     </row>
     <row r="191" spans="2:2">
       <c r="B191" s="14" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="192" spans="2:2">
       <c r="B192" s="14" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="193" spans="2:2">
       <c r="B193" s="14" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="14" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="14" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="14" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="14" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="198" spans="2:2">
       <c r="B198" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="202" spans="2:2" ht="18">
       <c r="B202" s="13" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="203" spans="2:2">
@@ -7407,72 +7854,72 @@
     </row>
     <row r="204" spans="2:2">
       <c r="B204" s="14" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="205" spans="2:2">
       <c r="B205" s="14" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="206" spans="2:2">
       <c r="B206" s="14" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="207" spans="2:2">
       <c r="B207" s="14" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="208" spans="2:2">
       <c r="B208" s="14" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="209" spans="2:2">
       <c r="B209" s="14" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="210" spans="2:2">
       <c r="B210" s="14" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="211" spans="2:2">
       <c r="B211" s="14" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="212" spans="2:2">
       <c r="B212" s="14" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="213" spans="2:2">
       <c r="B213" s="14" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="214" spans="2:2">
       <c r="B214" s="14" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="215" spans="2:2">
       <c r="B215" s="14" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="216" spans="2:2">
       <c r="B216" s="14" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="220" spans="2:2" ht="18">
       <c r="B220" s="13" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="221" spans="2:2">
@@ -7480,52 +7927,52 @@
     </row>
     <row r="222" spans="2:2">
       <c r="B222" s="14" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="223" spans="2:2">
       <c r="B223" s="14" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="224" spans="2:2">
       <c r="B224" s="14" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="225" spans="2:2">
       <c r="B225" s="14" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="226" spans="2:2">
       <c r="B226" s="14" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="227" spans="2:2">
       <c r="B227" s="14" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="228" spans="2:2">
       <c r="B228" s="14" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="229" spans="2:2">
       <c r="B229" s="14" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="230" spans="2:2">
       <c r="B230" s="14" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="234" spans="2:2" ht="18">
       <c r="B234" s="13" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="235" spans="2:2">
@@ -7533,57 +7980,57 @@
     </row>
     <row r="236" spans="2:2">
       <c r="B236" s="14" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="237" spans="2:2">
       <c r="B237" s="14" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="238" spans="2:2">
       <c r="B238" s="14" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="239" spans="2:2">
       <c r="B239" s="14" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="240" spans="2:2">
       <c r="B240" s="14" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="241" spans="2:2">
       <c r="B241" s="14" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="242" spans="2:2">
       <c r="B242" s="14" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="243" spans="2:2">
       <c r="B243" s="14" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="244" spans="2:2">
       <c r="B244" s="14" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="245" spans="2:2">
       <c r="B245" s="14" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="249" spans="2:2" ht="18">
       <c r="B249" s="13" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="250" spans="2:2">
@@ -7591,57 +8038,57 @@
     </row>
     <row r="251" spans="2:2">
       <c r="B251" s="14" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="252" spans="2:2">
       <c r="B252" s="14" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="253" spans="2:2">
       <c r="B253" s="14" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="254" spans="2:2">
       <c r="B254" s="14" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="255" spans="2:2">
       <c r="B255" s="14" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="256" spans="2:2">
       <c r="B256" s="14" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="257" spans="2:2">
       <c r="B257" s="14" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="258" spans="2:2">
       <c r="B258" s="14" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="259" spans="2:2">
       <c r="B259" s="14" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="260" spans="2:2">
       <c r="B260" s="14" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="264" spans="2:2" ht="18">
       <c r="B264" s="13" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="265" spans="2:2">
@@ -7649,77 +8096,257 @@
     </row>
     <row r="266" spans="2:2">
       <c r="B266" s="14" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="267" spans="2:2">
       <c r="B267" s="14" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="268" spans="2:2">
       <c r="B268" s="14" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="269" spans="2:2">
       <c r="B269" s="14" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="270" spans="2:2">
       <c r="B270" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="271" spans="2:2">
       <c r="B271" s="14" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="272" spans="2:2">
       <c r="B272" s="14" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="273" spans="2:2">
       <c r="B273" s="14" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="274" spans="2:2">
       <c r="B274" s="14" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="275" spans="2:2">
       <c r="B275" s="14" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="276" spans="2:2">
       <c r="B276" s="14" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="277" spans="2:2">
       <c r="B277" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="278" spans="2:2">
       <c r="B278" s="14" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="279" spans="2:2">
       <c r="B279" s="14" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="280" spans="2:2">
       <c r="B280" s="14" t="s">
-        <v>551</v>
+        <v>550</v>
+      </c>
+    </row>
+    <row r="282" spans="2:2">
+      <c r="B282" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="284" spans="2:2">
+      <c r="B284" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="285" spans="2:2">
+      <c r="B285" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="286" spans="2:2">
+      <c r="B286" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="287" spans="2:2">
+      <c r="B287" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="288" spans="2:2">
+      <c r="B288" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="289" spans="2:2">
+      <c r="B289" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="290" spans="2:2">
+      <c r="B290" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="291" spans="2:2">
+      <c r="B291" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="292" spans="2:2">
+      <c r="B292" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="293" spans="2:2">
+      <c r="B293" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="295" spans="2:2">
+      <c r="B295" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="297" spans="2:2">
+      <c r="B297" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="298" spans="2:2">
+      <c r="B298" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="299" spans="2:2">
+      <c r="B299" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="300" spans="2:2">
+      <c r="B300" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="302" spans="2:2">
+      <c r="B302" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="304" spans="2:2">
+      <c r="B304" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="305" spans="2:2">
+      <c r="B305" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="306" spans="2:2">
+      <c r="B306" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="307" spans="2:2">
+      <c r="B307" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="308" spans="2:2">
+      <c r="B308" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="309" spans="2:2">
+      <c r="B309" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="310" spans="2:2">
+      <c r="B310" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="311" spans="2:2">
+      <c r="B311" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="313" spans="2:2">
+      <c r="B313" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="315" spans="2:2">
+      <c r="B315" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="316" spans="2:2">
+      <c r="B316" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="317" spans="2:2">
+      <c r="B317" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="318" spans="2:2">
+      <c r="B318" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="319" spans="2:2">
+      <c r="B319" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="321" spans="2:2">
+      <c r="B321" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="323" spans="2:2">
+      <c r="B323" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="324" spans="2:2">
+      <c r="B324" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="325" spans="2:2">
+      <c r="B325" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="326" spans="2:2">
+      <c r="B326" t="s">
+        <v>679</v>
       </c>
     </row>
   </sheetData>
@@ -7741,48 +8368,115 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18945B75-7B01-4977-8367-724A01A18D2E}">
+  <dimension ref="B1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="3" max="3" width="40.44140625" customWidth="1"/>
+    <col min="4" max="4" width="18.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4" ht="15" thickBot="1"/>
+    <row r="2" spans="2:4" ht="15" thickBot="1">
+      <c r="B2" s="29"/>
+      <c r="C2" s="29" t="s">
+        <v>633</v>
+      </c>
+      <c r="D2" s="29"/>
+    </row>
+    <row r="3" spans="2:4" ht="114" customHeight="1" thickBot="1">
+      <c r="B3" s="29"/>
+      <c r="C3" s="29" t="s">
+        <v>634</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="135.6" customHeight="1" thickBot="1">
+      <c r="B4" s="29"/>
+      <c r="C4" s="29" t="s">
+        <v>636</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="241.8" customHeight="1" thickBot="1">
+      <c r="B5" s="29"/>
+      <c r="C5" s="29" t="s">
+        <v>638</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="58.2" thickBot="1">
+      <c r="B6" s="29"/>
+      <c r="C6" s="29" t="s">
+        <v>640</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="237" customHeight="1" thickBot="1">
+      <c r="B7" s="29"/>
+      <c r="C7" s="29" t="s">
+        <v>642</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>643</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A56F67A8-8B9F-47F1-AE02-7D1177177A32}">
   <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="15" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="16" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="17" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
